--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="875">
   <si>
     <t xml:space="preserve">Card ID</t>
   </si>
@@ -2166,6 +2166,489 @@
   </si>
   <si>
     <t xml:space="preserve">Soft disruption: bounce a key piece for a tempo hit (they redraw it, so it's not a two-for-one) and read their hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 damage to your opponent. Discard 1 random card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 damage to your opponent and give them 1 Burn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 damage to your opponent. They discard 1 random component.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, your damaging spells deal +1 damage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return up to 2 Verbal-providing components from your discard pile to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard 1 card. Deal 1 damage to your opponent for each symbol on it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take 1 damage. Deal 3 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 damage to your opponent. Draw 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 damage to your opponent and 2 damage to a Ward they control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 5 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 damage to your opponent. Reactions cannot target this spell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, deal 2 damage to them. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trap: when your opponent prevents or reduces damage you deal, deal 2 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trap: when your opponent attaches a Material (M) component to a prepared spell, deal 2 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent plays a Reaction, deal 4 damage to them. The Reaction still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 6 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 damage to your opponent. This damage cannot be reduced below 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 damage to your opponent and give them 2 Burn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 damage to your opponent. If they control a Ward, 1 of that damage hits the Ward instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard your hand. Deal 2 damage to your opponent for each card discarded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give your opponent 3 Burn. This round, their Burn also triggers at the start of your turns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, your damaging spells deal +2 damage and you take 1 damage at the start of each of your turns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 damage to your opponent. Draw 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 damage to your opponent for each component attached to their prepared spells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 damage to your opponent. This round, their Reactions cost 1 additional component to play.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 damage to your opponent, plus 1 for each Burn on them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, deal damage to them equal to its attached components. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell that requires a Material (M) component. Deal 2 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 damage to your opponent. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent plays a Reaction, deal 3 damage to them. The Reaction still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 7 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 damage to your opponent, then 2 damage to each Ward they control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 5 damage to your opponent. This spell cannot be cancelled, redirected or reduced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give your opponent 4 Burn. This round, each of their Burn deals 1 additional damage when it triggers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 damage to your opponent, plus 2 for each Reaction they have cast this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 damage to your opponent. Draw 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take 3 damage. Deal 8 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy all of your opponent's Wards. Deal damage to them equal to the HP those Wards had.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, whenever your opponent plays a Reaction, deal 3 damage to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, deal damage to them equal to twice its level. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When target spell deals damage to you, deal twice that damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell or Reaction, deal 6 damage to them. It still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 12 damage to your opponent. This spell cannot be cancelled, prevented, redirected or reduced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 6 damage to your opponent. This round, your damaging spells deal +2 damage and your Burn deals double.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When target spell deals damage to you, deal three times that damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top 3 cards of your deck; take 1, put the rest back on top. This round, spell damage dealt to you is reduced by 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top 2 cards of your deck; take 1, put the other on the bottom. Remove 1 Burn from yourself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prophecy (2 turns): destroy your opponent's largest Ward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 2 cards. If either is a multi-symbol component, draw a third.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return a component from your discard pile to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 damage to your opponent's weakest Ward. Look at the top 2 cards of your deck and put them back in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the components in your opponent's hand. They discard one of your choice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your opponent's largest Ward loses half its HP, rounded up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 1 card, then put a card from your hand on top of your deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 damage to your opponent. Look at their hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prophecy (2 turns): deal 2 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, draw 1 card and deal 1 damage to them. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return up to 2 components from your discard pile to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search your deck for a component and put it into your hand, then shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at your opponent's hand. Draw 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard any number of cards, then draw that many.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy target Ward or ongoing effect. Draw 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prophecy (2 turns): deal 4 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 2 cards, then put a card from your hand on top of your deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top 5 cards of your deck and put them back in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top 3 cards of your deck and put them back in any order. Prophecy (1 turn): deal 2 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return a component attached to target spell to its owner's hand. If the spell no longer meets its cost, cancel it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, draw 1 card. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirect target spell: it hits its caster instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cast a copy of a Level 1 spell you have already cast this round, without paying its cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shuffle your discard pile into your deck, then draw 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search your deck for any card and put it into your hand, then draw 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top 5 cards of your deck; take 2, put the rest back on top in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at your opponent's hand and the top 3 cards of their deck. Draw 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prophecy (3 turns): deal 7 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search your deck for up to 2 components and put them into your hand, then shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw until you have 7 cards in hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell. It returns to its owner's prepared spells sealed: it cannot be cast again this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell and return its components to its owner's hand. The spell returns to their prepared spells unspent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cast a copy of a Level 1 or 2 spell either player has cast this round, without paying its cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 2 cards. Deal 1 damage to your opponent for each card in your hand beyond 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at your opponent's hand. They discard a card of your choice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 4 cards. This turn, your spells cannot be cancelled or redirected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return every component from your discard pile to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search your deck for up to 3 cards and put them into your hand, then shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prophecy (3 turns): deal 9 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each player shuffles their hand and discard pile into their deck, then draws 5 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cast a copy of any spell cast this round, without paying its cost. You may cast 1 additional spell this turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top 2 cards of your deck; take 1, put the other back on top.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top card of your deck: a component goes to your hand, anything else to the bottom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard 1 card, then draw 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose a basic component in your hand. Until end of turn, treat it as a basic component of another symbol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return a component from your discard pile to the top of your deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The next damaging spell you cast this turn deals +1 damage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ward you control gains 2 HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard your hand, then draw 4 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard 1 card, then search your deck for any card and put it into your hand; shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search your deck for a same-symbol dual component (VV, SS or MM) and put it into your hand, then shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top 4 cards of your deck and put them back in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the top card of your deck: a component attaches to one of your prepared spells, anything else goes to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take 2 damage. This turn you may cast 1 additional spell, if you have a free slot and its components are attached.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take 2 damage. The next spell you cast this turn deals +3 damage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 3 HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy target Ward or ongoing effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove all Burn from yourself. Heal 1 for each Burn removed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your spells cannot be cancelled or redirected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your opponent cannot make you discard or strip your cards or components.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shuffle your discard pile into your deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your opponent cannot draw cards beyond their normal turn draw.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, whenever your opponent plays a Reaction, they take 2 damage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at your opponent's hand. You may put a component from it on top of their deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ward you control gains 2 HP (create a 2 HP Ward if you have none). Remove 1 Burn from yourself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 1 HP. If it is destroyed this round, draw 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each Ward you control gains 1 HP. If you control a Ward, deal 1 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, spells with only 1 component attached cannot target you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, spell damage dealt to you is reduced by 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target spell deals 1 less damage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target spell deals 1 less damage, or 2 less if you control a Ward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target spell deals 1 less damage. Draw 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trap: when your opponent attaches a component to a prepared spell, return that component to their hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seal target prepared spell your opponent controls: it cannot be cast this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prevent all damage from target spell. Heal half the damage prevented, rounded down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 3 HP. Whenever it absorbs damage, deal 1 damage to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove all components from target spell; if it no longer meets its cost, cancel it. Your opponent draws 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell. You may immediately attach 1 component from your hand to a prepared spell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell that requires a Material (M) component.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell that requires a Somatic (S) component.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your opponent cannot play Reactions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, your opponent's Reactions cost 1 additional component to play.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 2 HP. While it stands, Level 1 spells cannot target you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 3 HP. While it stands, the first time each round your opponent casts a spell, draw 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacrifice one of your Wards. Prevent all damage from target spell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 6 HP. This round, damage dealt to you is reduced by 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell. Your opponent cannot cast more spells this turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, spell damage that would hit you heals you instead (up to 5 HP).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each Ward you control gains 2 HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell. Deal 2 damage to your opponent for each component attached to it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 5 HP. When it is destroyed, create a Ward with 2 HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strip every component from your opponent's prepared spells; cancel target spell if it no longer meets its cost. They draw 1 card per spell stripped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 4 HP. This round, your opponent cannot target or destroy your Wards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy one of your Wards. Deal damage equal to its remaining HP to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal damage to your opponent equal to half your ledger, rounded up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 damage to your opponent for each Reaction you have played this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, whenever your opponent plays a Reaction, they take 3 damage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 5 damage to your opponent, or 7 if you control a Ward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacrifice all your Wards. Deal 2 damage to your opponent for each HP they had.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel target spell. Deal twice the damage it would have dealt to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 damage to your opponent. If they control a Ward, destroy it and deal 8 damage instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, spells cannot damage you and your opponent cannot play Reactions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Ward with 10 HP that your opponent cannot target or destroy. When it breaks, heal 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel every spell on the stack. Your opponent cannot cast spells this turn or play Reactions until the start of your next turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal damage to your opponent equal to your current HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 damage to your opponent for each round of this match so far.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel every spell your opponent has on the stack. Deal 3 damage to them for each spell cancelled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy every Ward on both sides. Deal 3 damage to your opponent for each Ward destroyed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend up to 4 from your ledger. Create a Ward with HP equal to the amount spent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 6 from your ledger to cancel target spell. Castable only with 6 or more banked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend up to 6 from your ledger. Heal half the amount spent, rounded down.</t>
   </si>
 </sst>
 </file>
@@ -2635,7 +3118,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>14</v>
+        <v>828</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="5" t="s">
@@ -2662,7 +3145,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>829</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="5" t="s">
@@ -2689,7 +3172,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>22</v>
+        <v>830</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="5" t="s">
@@ -2716,7 +3199,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>26</v>
+        <v>831</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="5" t="s">
@@ -2743,7 +3226,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>30</v>
+        <v>832</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="5" t="s">
@@ -2770,7 +3253,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>35</v>
+        <v>833</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="5" t="s">
@@ -2797,7 +3280,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>39</v>
+        <v>834</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="5" t="s">
@@ -2824,7 +3307,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>43</v>
+        <v>835</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="5" t="s">
@@ -2851,7 +3334,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>47</v>
+        <v>836</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="5" t="s">
@@ -2878,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>52</v>
+        <v>837</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="5" t="s">
@@ -2905,7 +3388,7 @@
         <v>51</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>56</v>
+        <v>838</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="5" t="s">
@@ -2932,7 +3415,7 @@
         <v>51</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>60</v>
+        <v>839</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="5" t="s">
@@ -2959,7 +3442,7 @@
         <v>51</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>64</v>
+        <v>840</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="5" t="s">
@@ -2986,7 +3469,7 @@
         <v>51</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>68</v>
+        <v>841</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="5" t="s">
@@ -3013,7 +3496,7 @@
         <v>72</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>73</v>
+        <v>842</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="5" t="s">
@@ -3040,7 +3523,7 @@
         <v>51</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>77</v>
+        <v>843</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="5" t="s">
@@ -3067,7 +3550,7 @@
         <v>51</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>81</v>
+        <v>844</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="5" t="s">
@@ -3094,7 +3577,7 @@
         <v>51</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>85</v>
+        <v>845</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="5" t="s">
@@ -3121,7 +3604,7 @@
         <v>51</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>89</v>
+        <v>846</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="5" t="s">
@@ -3148,7 +3631,7 @@
         <v>93</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>94</v>
+        <v>847</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="5" t="s">
@@ -3175,7 +3658,7 @@
         <v>51</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>98</v>
+        <v>848</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="5" t="s">
@@ -3202,7 +3685,7 @@
         <v>102</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>103</v>
+        <v>849</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="5" t="s">
@@ -3229,7 +3712,7 @@
         <v>102</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>107</v>
+        <v>850</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="5" t="s">
@@ -3256,7 +3739,7 @@
         <v>111</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>112</v>
+        <v>851</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="5" t="s">
@@ -3283,7 +3766,7 @@
         <v>102</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>116</v>
+        <v>852</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="5" t="s">
@@ -3310,7 +3793,7 @@
         <v>120</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>121</v>
+        <v>853</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="5" t="s">
@@ -3337,7 +3820,7 @@
         <v>111</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>125</v>
+        <v>854</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="5" t="s">
@@ -3364,7 +3847,7 @@
         <v>102</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>129</v>
+        <v>855</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="5" t="s">
@@ -3391,7 +3874,7 @@
         <v>102</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>133</v>
+        <v>856</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="5" t="s">
@@ -3418,7 +3901,7 @@
         <v>111</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>137</v>
+        <v>837</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="5" t="s">
@@ -3445,7 +3928,7 @@
         <v>102</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>141</v>
+        <v>857</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="5" t="s">
@@ -3472,7 +3955,7 @@
         <v>51</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>145</v>
+        <v>858</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="5" t="s">
@@ -3499,7 +3982,7 @@
         <v>111</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>149</v>
+        <v>859</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="5" t="s">
@@ -3526,7 +4009,7 @@
         <v>102</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>153</v>
+        <v>860</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="5" t="s">
@@ -3553,7 +4036,7 @@
         <v>102</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>157</v>
+        <v>861</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="5" t="s">
@@ -3580,7 +4063,7 @@
         <v>120</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>161</v>
+        <v>862</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="5" t="s">
@@ -3607,7 +4090,7 @@
         <v>102</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>165</v>
+        <v>863</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="5" t="s">
@@ -3634,7 +4117,7 @@
         <v>111</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>169</v>
+        <v>864</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="5" t="s">
@@ -3661,7 +4144,7 @@
         <v>173</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>174</v>
+        <v>865</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="5" t="s">
@@ -3688,7 +4171,7 @@
         <v>178</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>179</v>
+        <v>866</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="5" t="s">
@@ -3715,7 +4198,7 @@
         <v>173</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>183</v>
+        <v>867</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="5" t="s">
@@ -3742,7 +4225,7 @@
         <v>173</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>187</v>
+        <v>868</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="5" t="s">
@@ -3769,7 +4252,7 @@
         <v>178</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>191</v>
+        <v>869</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="5" t="s">
@@ -3796,7 +4279,7 @@
         <v>173</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>195</v>
+        <v>870</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="5" t="s">
@@ -3823,7 +4306,7 @@
         <v>173</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>199</v>
+        <v>871</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
@@ -3859,10 +4342,8 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>Spend up to 4 of the damage you have prevented this match. Create a Ward with HP equal to the amount spent.</t>
-        </is>
+      <c r="G47" s="5" t="s">
+        <v>872</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="5" t="inlineStr">
@@ -3900,10 +4381,8 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>Spend 6 of the damage you have prevented this match: cancel target spell. Castable only while you have at least 6 prevented.</t>
-        </is>
+      <c r="G48" s="5" t="s">
+        <v>873</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="5" t="inlineStr">
@@ -3941,10 +4420,8 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>Spend up to 6 of the damage you have prevented this match. Heal half the amount spent, rounded down.</t>
-        </is>
+      <c r="G49" s="5" t="s">
+        <v>874</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="5" t="inlineStr">
@@ -4032,7 +4509,7 @@
         <v>204</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>205</v>
+        <v>714</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="5" t="s">
@@ -4059,7 +4536,7 @@
         <v>204</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>209</v>
+        <v>715</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="5" t="s">
@@ -4086,7 +4563,7 @@
         <v>204</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>213</v>
+        <v>716</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="5" t="s">
@@ -4113,7 +4590,7 @@
         <v>204</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>217</v>
+        <v>717</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="5"/>
@@ -4138,7 +4615,7 @@
         <v>204</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>220</v>
+        <v>718</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="5"/>
@@ -4163,7 +4640,7 @@
         <v>204</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>223</v>
+        <v>719</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="5"/>
@@ -4188,7 +4665,7 @@
         <v>204</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>226</v>
+        <v>720</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="5" t="s">
@@ -4215,7 +4692,7 @@
         <v>204</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>230</v>
+        <v>721</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="5"/>
@@ -4240,7 +4717,7 @@
         <v>233</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>234</v>
+        <v>722</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="5" t="s">
@@ -4267,7 +4744,7 @@
         <v>204</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>238</v>
+        <v>723</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="5"/>
@@ -4292,7 +4769,7 @@
         <v>241</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>242</v>
+        <v>724</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="5"/>
@@ -4317,7 +4794,7 @@
         <v>241</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>245</v>
+        <v>725</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="5" t="s">
@@ -4344,7 +4821,7 @@
         <v>204</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>249</v>
+        <v>726</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="5"/>
@@ -4369,7 +4846,7 @@
         <v>204</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>252</v>
+        <v>727</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="5" t="s">
@@ -4396,7 +4873,7 @@
         <v>204</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>256</v>
+        <v>728</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="5" t="s">
@@ -4423,7 +4900,7 @@
         <v>241</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>260</v>
+        <v>729</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="5"/>
@@ -4448,7 +4925,7 @@
         <v>241</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>263</v>
+        <v>730</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="5" t="s">
@@ -4475,7 +4952,7 @@
         <v>241</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>267</v>
+        <v>731</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="5" t="s">
@@ -4502,7 +4979,7 @@
         <v>241</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>271</v>
+        <v>732</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="5"/>
@@ -4527,7 +5004,7 @@
         <v>241</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>274</v>
+        <v>733</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="5" t="s">
@@ -4554,7 +5031,7 @@
         <v>241</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>278</v>
+        <v>734</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="5" t="s">
@@ -4581,7 +5058,7 @@
         <v>241</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>282</v>
+        <v>735</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="5" t="s">
@@ -4608,7 +5085,7 @@
         <v>241</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>286</v>
+        <v>736</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="5" t="s">
@@ -4635,7 +5112,7 @@
         <v>233</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>290</v>
+        <v>737</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="5" t="s">
@@ -4662,7 +5139,7 @@
         <v>241</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>294</v>
+        <v>738</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="5" t="s">
@@ -4689,7 +5166,7 @@
         <v>93</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>298</v>
+        <v>739</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="5" t="s">
@@ -4716,7 +5193,7 @@
         <v>241</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>302</v>
+        <v>740</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="5" t="s">
@@ -4743,7 +5220,7 @@
         <v>241</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>306</v>
+        <v>741</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="5" t="s">
@@ -4770,7 +5247,7 @@
         <v>233</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>310</v>
+        <v>742</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="5" t="s">
@@ -4797,7 +5274,7 @@
         <v>241</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>314</v>
+        <v>743</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="5"/>
@@ -4822,7 +5299,7 @@
         <v>241</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>317</v>
+        <v>744</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="5" t="s">
@@ -4849,7 +5326,7 @@
         <v>321</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>322</v>
+        <v>745</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="5" t="s">
@@ -4876,7 +5353,7 @@
         <v>321</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>326</v>
+        <v>746</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="5" t="s">
@@ -4903,7 +5380,7 @@
         <v>321</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>330</v>
+        <v>734</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="5" t="s">
@@ -4930,7 +5407,7 @@
         <v>321</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>334</v>
+        <v>747</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="5" t="s">
@@ -4957,7 +5434,7 @@
         <v>321</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>338</v>
+        <v>748</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="5" t="s">
@@ -4984,7 +5461,7 @@
         <v>321</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>342</v>
+        <v>749</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="5" t="s">
@@ -5011,7 +5488,7 @@
         <v>346</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>347</v>
+        <v>750</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="5" t="s">
@@ -5038,7 +5515,7 @@
         <v>321</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>351</v>
+        <v>751</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="5" t="s">
@@ -5065,7 +5542,7 @@
         <v>321</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>355</v>
+        <v>752</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="5" t="s">
@@ -5092,7 +5569,7 @@
         <v>359</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>360</v>
+        <v>753</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="5" t="s">
@@ -5119,7 +5596,7 @@
         <v>321</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>364</v>
+        <v>754</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="5" t="s">
@@ -5146,7 +5623,7 @@
         <v>346</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>368</v>
+        <v>755</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="5"/>
@@ -5171,7 +5648,7 @@
         <v>321</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>371</v>
+        <v>756</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="5"/>
@@ -5196,7 +5673,7 @@
         <v>374</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>375</v>
+        <v>757</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
@@ -5223,7 +5700,7 @@
         <v>379</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>380</v>
+        <v>758</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="5" t="s">
@@ -5250,7 +5727,7 @@
         <v>384</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>385</v>
+        <v>759</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="5" t="s">
@@ -5336,7 +5813,7 @@
         <v>390</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>391</v>
+        <v>760</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="5" t="s">
@@ -5363,7 +5840,7 @@
         <v>390</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>395</v>
+        <v>761</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="5" t="s">
@@ -5390,7 +5867,7 @@
         <v>390</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>399</v>
+        <v>762</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="5" t="s">
@@ -5417,7 +5894,7 @@
         <v>390</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>403</v>
+        <v>763</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="5" t="s">
@@ -5444,7 +5921,7 @@
         <v>390</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>407</v>
+        <v>764</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="5" t="s">
@@ -5471,7 +5948,7 @@
         <v>390</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>411</v>
+        <v>765</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="5" t="s">
@@ -5498,7 +5975,7 @@
         <v>390</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>415</v>
+        <v>766</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="5" t="s">
@@ -5525,7 +6002,7 @@
         <v>390</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>419</v>
+        <v>767</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="5" t="s">
@@ -5552,7 +6029,7 @@
         <v>390</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>423</v>
+        <v>768</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="5" t="s">
@@ -5579,7 +6056,7 @@
         <v>390</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>427</v>
+        <v>769</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="5" t="s">
@@ -5606,7 +6083,7 @@
         <v>390</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>431</v>
+        <v>770</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="5" t="s">
@@ -5633,7 +6110,7 @@
         <v>447</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>435</v>
+        <v>771</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="5" t="s">
@@ -5687,7 +6164,7 @@
         <v>390</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>443</v>
+        <v>772</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="5" t="s">
@@ -5714,7 +6191,7 @@
         <v>447</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>448</v>
+        <v>773</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="5" t="s">
@@ -5741,7 +6218,7 @@
         <v>447</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>452</v>
+        <v>774</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="5" t="s">
@@ -5768,7 +6245,7 @@
         <v>447</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>456</v>
+        <v>775</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="5" t="s">
@@ -5795,7 +6272,7 @@
         <v>447</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>460</v>
+        <v>776</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="5" t="s">
@@ -5822,7 +6299,7 @@
         <v>447</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>464</v>
+        <v>777</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="5" t="s">
@@ -5849,7 +6326,7 @@
         <v>447</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>468</v>
+        <v>778</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="5" t="s">
@@ -5876,7 +6353,7 @@
         <v>447</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>472</v>
+        <v>779</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="5" t="s">
@@ -5903,7 +6380,7 @@
         <v>447</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>476</v>
+        <v>780</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="5" t="s">
@@ -5930,7 +6407,7 @@
         <v>447</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>480</v>
+        <v>781</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="5" t="s">
@@ -5957,7 +6434,7 @@
         <v>447</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>484</v>
+        <v>782</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="5" t="s">
@@ -5984,7 +6461,7 @@
         <v>447</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>488</v>
+        <v>783</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="5" t="s">
@@ -6011,7 +6488,7 @@
         <v>492</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>493</v>
+        <v>784</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="5" t="s">
@@ -6038,7 +6515,7 @@
         <v>497</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>498</v>
+        <v>785</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="5" t="s">
@@ -6065,7 +6542,7 @@
         <v>502</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>503</v>
+        <v>786</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="5" t="s">
@@ -6092,7 +6569,7 @@
         <v>502</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>507</v>
+        <v>787</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="5" t="s">
@@ -6119,7 +6596,7 @@
         <v>502</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>511</v>
+        <v>788</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="5" t="s">
@@ -6146,7 +6623,7 @@
         <v>502</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>515</v>
+        <v>789</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="5" t="s">
@@ -6173,7 +6650,7 @@
         <v>502</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>519</v>
+        <v>790</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="5" t="s">
@@ -6200,7 +6677,7 @@
         <v>502</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>523</v>
+        <v>791</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="5" t="s">
@@ -6227,7 +6704,7 @@
         <v>502</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>527</v>
+        <v>792</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="5" t="s">
@@ -6254,7 +6731,7 @@
         <v>502</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>531</v>
+        <v>793</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="5" t="s">
@@ -6281,7 +6758,7 @@
         <v>502</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>535</v>
+        <v>794</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="5" t="s">
@@ -6308,7 +6785,7 @@
         <v>539</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>540</v>
+        <v>795</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="5" t="s">
@@ -6335,7 +6812,7 @@
         <v>539</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>544</v>
+        <v>796</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="5" t="s">
@@ -6362,7 +6839,7 @@
         <v>548</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>549</v>
+        <v>797</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="5" t="s">
@@ -6389,7 +6866,7 @@
         <v>553</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>554</v>
+        <v>798</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="5" t="s">
@@ -6416,7 +6893,7 @@
         <v>553</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>558</v>
+        <v>799</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="5" t="s">
@@ -6443,7 +6920,7 @@
         <v>553</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>562</v>
+        <v>800</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="5" t="s">
@@ -6470,7 +6947,7 @@
         <v>553</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>566</v>
+        <v>801</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="5" t="s">
@@ -6497,7 +6974,7 @@
         <v>553</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>570</v>
+        <v>802</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="5" t="s">
@@ -6524,7 +7001,7 @@
         <v>574</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>575</v>
+        <v>803</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
@@ -6606,7 +7083,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="5" t="s">
-        <v>581</v>
+        <v>804</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>582</v>
@@ -6631,7 +7108,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="5" t="s">
-        <v>586</v>
+        <v>805</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>587</v>
@@ -6656,7 +7133,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5" t="s">
-        <v>591</v>
+        <v>769</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>587</v>
@@ -6681,7 +7158,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="5" t="s">
-        <v>595</v>
+        <v>806</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>596</v>
@@ -6706,7 +7183,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="5" t="s">
-        <v>600</v>
+        <v>807</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>601</v>
@@ -6731,7 +7208,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="5" t="s">
-        <v>605</v>
+        <v>808</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>606</v>
@@ -6756,7 +7233,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="5" t="s">
-        <v>610</v>
+        <v>809</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>611</v>
@@ -6781,7 +7258,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="5" t="s">
-        <v>615</v>
+        <v>810</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>616</v>
@@ -6865,7 +7342,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="5" t="s">
-        <v>621</v>
+        <v>779</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>622</v>
@@ -6890,7 +7367,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="5" t="s">
-        <v>626</v>
+        <v>811</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>627</v>
@@ -6915,7 +7392,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5" t="s">
-        <v>631</v>
+        <v>812</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>582</v>
@@ -6940,7 +7417,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="5" t="s">
-        <v>635</v>
+        <v>813</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>636</v>
@@ -6965,7 +7442,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="5" t="s">
-        <v>411</v>
+        <v>765</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>606</v>
@@ -6990,7 +7467,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="5" t="s">
-        <v>643</v>
+        <v>814</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>644</v>
@@ -7015,7 +7492,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="5" t="s">
-        <v>648</v>
+        <v>815</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>649</v>
@@ -7040,7 +7517,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="5" t="s">
-        <v>653</v>
+        <v>816</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>654</v>
@@ -7065,7 +7542,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="5" t="s">
-        <v>658</v>
+        <v>817</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>659</v>
@@ -7090,7 +7567,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="5" t="s">
-        <v>663</v>
+        <v>818</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>611</v>
@@ -7115,7 +7592,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="5" t="s">
-        <v>667</v>
+        <v>819</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>668</v>
@@ -7140,7 +7617,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="5" t="s">
-        <v>672</v>
+        <v>820</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>673</v>
@@ -7165,7 +7642,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="5" t="s">
-        <v>677</v>
+        <v>821</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>678</v>
@@ -7190,7 +7667,7 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="5" t="s">
-        <v>682</v>
+        <v>822</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>683</v>
@@ -7215,7 +7692,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="5" t="s">
-        <v>687</v>
+        <v>823</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>688</v>
@@ -7240,7 +7717,7 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="5" t="s">
-        <v>692</v>
+        <v>824</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>693</v>
@@ -7265,7 +7742,7 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="5" t="s">
-        <v>697</v>
+        <v>825</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>698</v>
@@ -7290,7 +7767,7 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="5" t="s">
-        <v>702</v>
+        <v>826</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>683</v>
@@ -7315,7 +7792,7 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="5" t="s">
-        <v>706</v>
+        <v>771</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>707</v>
@@ -7340,7 +7817,7 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="5" t="s">
-        <v>711</v>
+        <v>827</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>712</v>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="1116">
   <si>
     <t xml:space="preserve">Card ID</t>
   </si>
@@ -2649,6 +2649,729 @@
   </si>
   <si>
     <t xml:space="preserve">Spend up to 6 from your ledger. Heal half the amount spent, rounded down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kindling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinder Snap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flashover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spreading Blaze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blazing Wrath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyromancer's Retort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flavor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every blaze that ever ate a city began as something this small.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thrown, not aimed. Aiming is for people with time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rune is spoken into the palm. The palm remembers it for days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One syllable, and the reagent in their hand is ash.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinder says the trick is not more fire. It is less patience.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What burned once will burn again, if you ask it nicely.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feed it anything. It is not particular.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rune bites the caster first. That is how you know it is loaded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry wood, a breath, and the lesson arrives on its own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A flick of ember at the ward, a flick at the wizard. Both notice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A line of fire with a point on it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoken too quickly to be answered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the door to cast, and the room comes out to meet you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn the blow aside if you like. The heat goes where it pleases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reagents are flammable. Cinder considers this their best quality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interrupt her and she stops being polite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The oldest argument in the duel circle, and still the loudest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hot enough that there is nothing left to insulate against.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It does not finish when the spell does.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pointed at the wizard. The ward only gets what spills.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything in the hand, all at once, and no regrets until later.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire does not keep a schedule. Now neither does theirs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The flame rides your breath for a round. It takes a toll each morning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A proper tantrum, with something learned from it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every component they laid out is a wick waiting to be lit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loud enough that answering costs them something.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The moment a smoldering room becomes a burning one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The more they loaded onto the spell, the more there is to burn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reagents catch. The spell they were feeding goes with them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She does not stop your spell. She simply answers it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reacting is a kind of breathing. Breathing feeds fire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Late Sun throws something down. Nobody asks why.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It finds the wizard first, then everything they built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The hand is fuel. Cinder has never thought of it any other way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some fires cannot be argued with.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each ember remembers it was once a bonfire, and tries to be one again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every answer they gave the fire, the fire took personally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burn the ground, then read what grows in it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take the burn yourself. It is the only way to be sure it is hot enough.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ward does not melt. It simply has nowhere to put the light.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawn on the floor of the circle. It listens for Reactions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The bigger the spell they speak, the bigger the room it burns in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What reaches her comes back doubled and still glowing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grandmother lights her pipe. The rest of the circle lights itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is no ward for this. There is barely a word for it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire that rises is fire that has decided not to stop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit her once and she will show you what you meant, three times over.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamplight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read the Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinch the Wick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omen of Ash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scent of Smoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sift the Ashes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scorch the Seam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Char the Page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat Fracture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candle's Eye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lantern Glare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke Omen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flicker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the Ashes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moth to Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read by Firelight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feed the Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burn Through</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slow Match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallow Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke Reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short Wick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull the Fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read the Sparks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flame Mirror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afterglow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekindle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamp in the Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury of Embers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything Illuminated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Pyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gather Kindling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonfire Vigil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unburnt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catch the Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overfed Lamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burn the Letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eye of the Blaze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rise from Ash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamplighter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ash Fall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flashpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two more pages, read by a flame that knows what is on them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The flame leans toward what comes next, and away from what hurts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trim the flame, read what the smoke left, and burn a little less.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The lamp shows their largest ward already as a drift of ash.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You smell what is coming before you see it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whatever burned, something of it is still in the pan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find the weakest ward and hold the candle to the join.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read their hand by candle, and let one page catch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat a ward unevenly and it splits along its own flaw.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A single flame, a single card, and a choice of what stays on top.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold the lantern up. It hurts their eyes and shows you their hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The smoke makes a shape. In two turns, the shape arrives.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The flame jumps when they cast. The seer reads the jump.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The pan still holds what you need. Two pieces of it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The one component you wanted comes to the light on its own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their hand, open on the table, and a page of your own turned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give the lamp what you do not need. It returns the same weight in light.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold the flame to the ward until it goes, and read the ash after.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cord lit now, burning down toward a thing that is already decided.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two pages by tallow light, and one set back for the morning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five curls of smoke, and the seer orders them as they please.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The candle is nearly out. Next turn, it finishes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take one piece from under the spell and see if it still stands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every spell they speak throws sparks. Each spark is a page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The lamp shows them their own spell, and the spell believes it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A spell already cast still glows. Warm it and cast it again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rake the whole ash pan back into the lamp and read on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold the lamp to the deck and the card you need is already lit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five embers, two of them worth keeping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their hand, the top of their deck, and nothing left in shadow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stacked now. Lit in three turns. The seer has already seen the smoke.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two components from the deck, before the fire needs them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sit by it until the hand is full.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A damp cloth over the spell, and it sleeps sealed until the round ends.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The match was never struck. The components were never spent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A spell lit once, on either side of the circle, can be lit from again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Too much oil and the lamp spits. Every spare page is a burn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read their hand, choose a page, and hold it to the flame.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For one turn the seer sees everything, and nothing can put the lamp out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every component that ever burned, back in the hand at once.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk the deck with a taper and light the three you came for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nine turns of damage in three. The lamp goes out when it lands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both hands, both ash pans, back into the lamps. Everyone starts again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any spell cast this round, lit again from the same flame, and one more besides.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinder Crust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bellows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat Shimmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ash Mantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firebrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooling Draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spark Arrester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron Brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swallow the Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searing Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Douse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snuff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Char the Reagent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scalding Grip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furnace Roar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stifling Heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilnwarden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watchfire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slag Sacrifice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hearth Eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salamander's Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reforge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammerfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ember Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scatter the Coals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forgewall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welded Shut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap the Furnace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammer Rhythm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scalding Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branding Iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meltdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anvil's Answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilnbreaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold Iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Adamant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Quench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrath of the Forge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long Firing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flashquench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shatter the Kilns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banked Coals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furnace Verdict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hearth's Warmth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel is not strong until it has been through the fire and out again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A thin shell of cooled slag. When it cracks, it tells you something.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every ward grows a little hotter, and one breath escapes toward the foe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small spells lose their aim in the air above a furnace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cloak of cold ash. It takes the edge off anything that lands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rake the coals over and the flame has less to feed on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiln brick turns heat. It turns more when the kiln is standing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the flue, let the heat out, and look at what the draft brings in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A mesh over the chimney. What they throw on comes straight back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressed hot against the page. The spell cannot be spoken past the mark.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berenice takes the whole blast in and keeps half of it as warmth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch the wall and the wall touches back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull the fuel from under the spell and watch it gutter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinched out between finger and thumb, with the other hand already moving.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A spell is only as whole as the ingredients it stands on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The gesture half-formed, the fingers already blistering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing can be heard over a forge at full heat. Nothing can be answered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The air is too thick to react in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A squat ward of fired clay. Small things do not get past it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lit on the wall. When the enemy moves, it tells you first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break the crust to save the metal underneath.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The oldest fire in the house. It has never once gone out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The spell dies on the tongue, and nothing lights behind it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The creature that lives in the forge and thinks of fire as a bath.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back into the fire, out again stronger. Every ward on the wall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything they piled onto the spell goes under the hammer with it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break the coal and there is still a live ember inside it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kick the fire apart and nothing on it stays lit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While it stands, nothing of theirs reaches the wards behind it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sealed with a bead of molten iron. Not this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the furnace and the melt goes where you point it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every blow the forge turned aside, it kept as heat. This is the heat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each Reaction was a stroke on the anvil. Here is what was made.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The circle is a kiln. Every answer they give costs them skin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hot from the forge. Hotter if the kiln is lit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every ward on the wall, poured out at once.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strike the anvil and the anvil strikes back harder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built for walls. Finds them, and is glad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The one metal magic will not touch. For a round, she is made of it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berenice's epithet, earned. Nothing has ever gone through.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything on the stack hisses out at once, and the circle goes quiet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every point of her that still stands, delivered as heat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A kiln fired for rounds on end. Open it and see what it made.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their whole stack, dropped in the water trough together.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every ward on the circle, hers and theirs, broken for the heat inside.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat set aside earlier, raked back into a wall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She spends banked heat to end the argument.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat saved from old blows, spent now on the body that took them.</t>
   </si>
 </sst>
 </file>
@@ -3055,7 +3778,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -3097,13 +3820,19 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>1021</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>11</v>
@@ -3124,13 +3853,19 @@
       <c r="I2" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="J2" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>1068</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>1022</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
@@ -3151,13 +3886,19 @@
       <c r="I3" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>1069</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>1023</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
@@ -3178,13 +3919,19 @@
       <c r="I4" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="J4" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>1070</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>1024</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
@@ -3205,13 +3952,19 @@
       <c r="I5" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="J5" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>29</v>
+        <v>1025</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>11</v>
@@ -3232,13 +3985,19 @@
       <c r="I6" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="J6" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>1072</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>1026</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>11</v>
@@ -3259,13 +4018,19 @@
       <c r="I7" s="5" t="s">
         <v>36</v>
       </c>
+      <c r="J7" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>1073</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>1027</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>11</v>
@@ -3286,13 +4051,19 @@
       <c r="I8" s="5" t="s">
         <v>40</v>
       </c>
+      <c r="J8" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>1074</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>1028</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>11</v>
@@ -3313,13 +4084,19 @@
       <c r="I9" s="5" t="s">
         <v>44</v>
       </c>
+      <c r="J9" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>1075</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>46</v>
+        <v>1029</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
@@ -3340,13 +4117,19 @@
       <c r="I10" s="5" t="s">
         <v>48</v>
       </c>
+      <c r="J10" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>1076</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>1030</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
@@ -3367,13 +4150,19 @@
       <c r="I11" s="5" t="s">
         <v>53</v>
       </c>
+      <c r="J11" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>1077</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>1031</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>11</v>
@@ -3394,13 +4183,19 @@
       <c r="I12" s="5" t="s">
         <v>57</v>
       </c>
+      <c r="J12" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>1078</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>59</v>
+        <v>1032</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>11</v>
@@ -3421,13 +4216,19 @@
       <c r="I13" s="5" t="s">
         <v>61</v>
       </c>
+      <c r="J13" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>1079</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>1033</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>11</v>
@@ -3448,13 +4249,19 @@
       <c r="I14" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="J14" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>1080</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>67</v>
+        <v>1034</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
@@ -3475,13 +4282,19 @@
       <c r="I15" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="J15" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>1081</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>71</v>
+        <v>1035</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>11</v>
@@ -3502,13 +4315,19 @@
       <c r="I16" s="5" t="s">
         <v>74</v>
       </c>
+      <c r="J16" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>1036</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
@@ -3529,13 +4348,19 @@
       <c r="I17" s="5" t="s">
         <v>78</v>
       </c>
+      <c r="J17" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>1083</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>1037</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
@@ -3556,13 +4381,19 @@
       <c r="I18" s="5" t="s">
         <v>82</v>
       </c>
+      <c r="J18" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>1084</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>84</v>
+        <v>1038</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>11</v>
@@ -3583,13 +4414,19 @@
       <c r="I19" s="5" t="s">
         <v>86</v>
       </c>
+      <c r="J19" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>1085</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>88</v>
+        <v>1039</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>11</v>
@@ -3610,13 +4447,19 @@
       <c r="I20" s="5" t="s">
         <v>90</v>
       </c>
+      <c r="J20" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>92</v>
+        <v>1040</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>11</v>
@@ -3637,13 +4480,19 @@
       <c r="I21" s="5" t="s">
         <v>95</v>
       </c>
+      <c r="J21" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>97</v>
+        <v>1041</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>11</v>
@@ -3664,13 +4513,19 @@
       <c r="I22" s="5" t="s">
         <v>99</v>
       </c>
+      <c r="J22" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>1088</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>101</v>
+        <v>1042</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>11</v>
@@ -3691,13 +4546,19 @@
       <c r="I23" s="5" t="s">
         <v>104</v>
       </c>
+      <c r="J23" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>1089</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>106</v>
+        <v>1043</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>11</v>
@@ -3718,13 +4579,19 @@
       <c r="I24" s="5" t="s">
         <v>108</v>
       </c>
+      <c r="J24" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>1090</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>110</v>
+        <v>1044</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>11</v>
@@ -3745,13 +4612,19 @@
       <c r="I25" s="5" t="s">
         <v>113</v>
       </c>
+      <c r="J25" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>1091</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>115</v>
+        <v>1045</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>11</v>
@@ -3772,13 +4645,19 @@
       <c r="I26" s="5" t="s">
         <v>117</v>
       </c>
+      <c r="J26" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>1092</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>119</v>
+        <v>1046</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>11</v>
@@ -3799,13 +4678,19 @@
       <c r="I27" s="5" t="s">
         <v>122</v>
       </c>
+      <c r="J27" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>1093</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>124</v>
+        <v>1047</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>11</v>
@@ -3826,13 +4711,19 @@
       <c r="I28" s="5" t="s">
         <v>126</v>
       </c>
+      <c r="J28" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>1094</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>128</v>
+        <v>1048</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>11</v>
@@ -3853,13 +4744,19 @@
       <c r="I29" s="5" t="s">
         <v>130</v>
       </c>
+      <c r="J29" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>1095</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>132</v>
+        <v>1049</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>11</v>
@@ -3880,13 +4777,19 @@
       <c r="I30" s="5" t="s">
         <v>134</v>
       </c>
+      <c r="J30" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>136</v>
+        <v>1050</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>11</v>
@@ -3907,13 +4810,19 @@
       <c r="I31" s="5" t="s">
         <v>138</v>
       </c>
+      <c r="J31" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>1097</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>140</v>
+        <v>1051</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>11</v>
@@ -3934,6 +4843,12 @@
       <c r="I32" s="5" t="s">
         <v>142</v>
       </c>
+      <c r="J32" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>1098</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
@@ -3961,13 +4876,19 @@
       <c r="I33" s="5" t="s">
         <v>146</v>
       </c>
+      <c r="J33" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>1099</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>148</v>
+        <v>1052</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>11</v>
@@ -3988,13 +4909,19 @@
       <c r="I34" s="5" t="s">
         <v>150</v>
       </c>
+      <c r="J34" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>152</v>
+        <v>1053</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>11</v>
@@ -4015,13 +4942,19 @@
       <c r="I35" s="5" t="s">
         <v>154</v>
       </c>
+      <c r="J35" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>1101</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>156</v>
+        <v>1054</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>11</v>
@@ -4042,13 +4975,19 @@
       <c r="I36" s="5" t="s">
         <v>158</v>
       </c>
+      <c r="J36" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>1102</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>160</v>
+        <v>1055</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>11</v>
@@ -4069,13 +5008,19 @@
       <c r="I37" s="5" t="s">
         <v>162</v>
       </c>
+      <c r="J37" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>164</v>
+        <v>1056</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>11</v>
@@ -4096,13 +5041,19 @@
       <c r="I38" s="5" t="s">
         <v>166</v>
       </c>
+      <c r="J38" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>1104</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>168</v>
+        <v>1057</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>11</v>
@@ -4123,13 +5074,19 @@
       <c r="I39" s="5" t="s">
         <v>170</v>
       </c>
+      <c r="J39" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>1105</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>171</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>172</v>
+        <v>1058</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>11</v>
@@ -4150,13 +5107,19 @@
       <c r="I40" s="5" t="s">
         <v>175</v>
       </c>
+      <c r="J40" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>1106</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>176</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>177</v>
+        <v>1059</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>11</v>
@@ -4177,13 +5140,19 @@
       <c r="I41" s="5" t="s">
         <v>180</v>
       </c>
+      <c r="J41" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>1107</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>181</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>182</v>
+        <v>1060</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>11</v>
@@ -4204,13 +5173,19 @@
       <c r="I42" s="5" t="s">
         <v>184</v>
       </c>
+      <c r="J42" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>1108</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>186</v>
+        <v>1061</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>11</v>
@@ -4231,13 +5206,19 @@
       <c r="I43" s="5" t="s">
         <v>188</v>
       </c>
+      <c r="J43" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>1109</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
         <v>189</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>190</v>
+        <v>1062</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>11</v>
@@ -4258,13 +5239,19 @@
       <c r="I44" s="5" t="s">
         <v>192</v>
       </c>
+      <c r="J44" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>1110</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>193</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>194</v>
+        <v>1063</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>11</v>
@@ -4285,13 +5272,19 @@
       <c r="I45" s="5" t="s">
         <v>196</v>
       </c>
+      <c r="J45" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>198</v>
+        <v>1064</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>11</v>
@@ -4311,6 +5304,12 @@
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
         <v>200</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1112</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4319,10 +5318,8 @@
           <t>ABJ-046</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Warding Tithe</t>
-        </is>
+      <c r="B47" s="3" t="s">
+        <v>1065</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
@@ -4351,6 +5348,12 @@
           <t>Ledger family (2026-08-13). Spends the Reckoning bank for tempo - every point spent is a point the late nuke loses. Gives prevention a use against doom decks that never touch wards.</t>
         </is>
       </c>
+      <c r="J47" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="inlineStr">
@@ -4358,10 +5361,8 @@
           <t>ABJ-047</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Sealed Verdict</t>
-        </is>
+      <c r="B48" s="3" t="s">
+        <v>1066</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
@@ -4390,6 +5391,12 @@
           <t>Ledger family. A cancel funded by the bank instead of scarce attached fuel - the extra answer per round Abjuration lacked against multi-doom turns.</t>
         </is>
       </c>
+      <c r="J48" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="inlineStr">
@@ -4397,10 +5404,8 @@
           <t>ABJ-048</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Restoring Rune</t>
-        </is>
+      <c r="B49" s="3" t="s">
+        <v>1067</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
@@ -4428,6 +5433,12 @@
         <is>
           <t>Ledger family. Sustain option - trades future Reckoning payload for present HP.</t>
         </is>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>1115</v>
       </c>
     </row>
   </sheetData>
@@ -4446,7 +5457,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -4488,6 +5499,12 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -4515,6 +5532,12 @@
       <c r="I2" s="5" t="s">
         <v>206</v>
       </c>
+      <c r="J2" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>886</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -4542,6 +5565,12 @@
       <c r="I3" s="5" t="s">
         <v>210</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>887</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -4569,6 +5598,12 @@
       <c r="I4" s="5" t="s">
         <v>214</v>
       </c>
+      <c r="J4" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>888</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -4594,6 +5629,12 @@
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="5"/>
+      <c r="J5" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -4619,6 +5660,12 @@
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>890</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -4644,6 +5691,12 @@
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="5"/>
+      <c r="J7" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -4671,6 +5724,12 @@
       <c r="I8" s="5" t="s">
         <v>227</v>
       </c>
+      <c r="J8" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -4696,13 +5755,19 @@
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="5"/>
+      <c r="J9" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>893</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>231</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>232</v>
+        <v>875</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>203</v>
@@ -4723,13 +5788,19 @@
       <c r="I10" s="5" t="s">
         <v>235</v>
       </c>
+      <c r="J10" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>237</v>
+        <v>876</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>203</v>
@@ -4748,6 +5819,12 @@
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="5"/>
+      <c r="J11" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>895</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -4773,6 +5850,12 @@
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="5"/>
+      <c r="J12" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>896</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -4800,6 +5883,12 @@
       <c r="I13" s="5" t="s">
         <v>246</v>
       </c>
+      <c r="J13" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>897</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -4825,6 +5914,12 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="5"/>
+      <c r="J14" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
@@ -4852,6 +5947,12 @@
       <c r="I15" s="5" t="s">
         <v>253</v>
       </c>
+      <c r="J15" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>899</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
@@ -4879,6 +5980,12 @@
       <c r="I16" s="5" t="s">
         <v>257</v>
       </c>
+      <c r="J16" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>900</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
@@ -4904,6 +6011,12 @@
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="5"/>
+      <c r="J17" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>901</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
@@ -4931,13 +6044,19 @@
       <c r="I18" s="5" t="s">
         <v>264</v>
       </c>
+      <c r="J18" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>266</v>
+        <v>877</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>203</v>
@@ -4958,6 +6077,12 @@
       <c r="I19" s="5" t="s">
         <v>268</v>
       </c>
+      <c r="J19" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>903</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
@@ -4983,6 +6108,12 @@
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="5"/>
+      <c r="J20" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>904</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -5010,6 +6141,12 @@
       <c r="I21" s="5" t="s">
         <v>275</v>
       </c>
+      <c r="J21" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>905</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
@@ -5037,6 +6174,12 @@
       <c r="I22" s="5" t="s">
         <v>279</v>
       </c>
+      <c r="J22" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>906</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -5064,6 +6207,12 @@
       <c r="I23" s="5" t="s">
         <v>283</v>
       </c>
+      <c r="J23" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>907</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -5091,6 +6240,12 @@
       <c r="I24" s="5" t="s">
         <v>287</v>
       </c>
+      <c r="J24" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>908</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -5118,6 +6273,12 @@
       <c r="I25" s="5" t="s">
         <v>291</v>
       </c>
+      <c r="J25" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>909</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
@@ -5145,6 +6306,12 @@
       <c r="I26" s="5" t="s">
         <v>295</v>
       </c>
+      <c r="J26" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
@@ -5172,13 +6339,19 @@
       <c r="I27" s="5" t="s">
         <v>299</v>
       </c>
+      <c r="J27" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>911</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>301</v>
+        <v>878</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>203</v>
@@ -5199,6 +6372,12 @@
       <c r="I28" s="5" t="s">
         <v>303</v>
       </c>
+      <c r="J28" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>912</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -5226,6 +6405,12 @@
       <c r="I29" s="5" t="s">
         <v>307</v>
       </c>
+      <c r="J29" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>913</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -5253,6 +6438,12 @@
       <c r="I30" s="5" t="s">
         <v>311</v>
       </c>
+      <c r="J30" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
@@ -5278,6 +6469,12 @@
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="5"/>
+      <c r="J31" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>915</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
@@ -5305,6 +6502,12 @@
       <c r="I32" s="5" t="s">
         <v>318</v>
       </c>
+      <c r="J32" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
@@ -5332,13 +6535,19 @@
       <c r="I33" s="5" t="s">
         <v>323</v>
       </c>
+      <c r="J33" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>324</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>325</v>
+        <v>879</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>203</v>
@@ -5359,6 +6568,12 @@
       <c r="I34" s="5" t="s">
         <v>327</v>
       </c>
+      <c r="J34" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
@@ -5386,6 +6601,12 @@
       <c r="I35" s="5" t="s">
         <v>331</v>
       </c>
+      <c r="J35" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
@@ -5413,6 +6634,12 @@
       <c r="I36" s="5" t="s">
         <v>335</v>
       </c>
+      <c r="J36" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
@@ -5440,13 +6667,19 @@
       <c r="I37" s="5" t="s">
         <v>339</v>
       </c>
+      <c r="J37" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>341</v>
+        <v>880</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>203</v>
@@ -5467,6 +6700,12 @@
       <c r="I38" s="5" t="s">
         <v>343</v>
       </c>
+      <c r="J38" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>922</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
@@ -5494,13 +6733,19 @@
       <c r="I39" s="5" t="s">
         <v>348</v>
       </c>
+      <c r="J39" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>349</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>350</v>
+        <v>881</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>203</v>
@@ -5521,6 +6766,12 @@
       <c r="I40" s="5" t="s">
         <v>352</v>
       </c>
+      <c r="J40" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>924</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
@@ -5548,6 +6799,12 @@
       <c r="I41" s="5" t="s">
         <v>356</v>
       </c>
+      <c r="J41" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
@@ -5575,6 +6832,12 @@
       <c r="I42" s="5" t="s">
         <v>361</v>
       </c>
+      <c r="J42" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
@@ -5602,6 +6865,12 @@
       <c r="I43" s="5" t="s">
         <v>365</v>
       </c>
+      <c r="J43" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
@@ -5627,6 +6896,12 @@
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="5"/>
+      <c r="J44" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>928</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
@@ -5652,6 +6927,12 @@
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="5"/>
+      <c r="J45" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
@@ -5679,6 +6960,12 @@
       <c r="I46" s="5" t="s">
         <v>376</v>
       </c>
+      <c r="J46" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
@@ -5706,13 +6993,19 @@
       <c r="I47" s="5" t="s">
         <v>381</v>
       </c>
+      <c r="J47" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>382</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>383</v>
+        <v>882</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>203</v>
@@ -5732,6 +7025,12 @@
       <c r="H48" s="6"/>
       <c r="I48" s="5" t="s">
         <v>386</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>932</v>
       </c>
     </row>
   </sheetData>
@@ -5750,7 +7049,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -5792,13 +7091,19 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>387</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>388</v>
+        <v>933</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>389</v>
@@ -5819,13 +7124,19 @@
       <c r="I2" s="5" t="s">
         <v>392</v>
       </c>
+      <c r="J2" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>393</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>394</v>
+        <v>934</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>389</v>
@@ -5846,13 +7157,19 @@
       <c r="I3" s="5" t="s">
         <v>396</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>397</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>398</v>
+        <v>935</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>389</v>
@@ -5873,13 +7190,19 @@
       <c r="I4" s="5" t="s">
         <v>400</v>
       </c>
+      <c r="J4" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>401</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>402</v>
+        <v>936</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>389</v>
@@ -5900,13 +7223,19 @@
       <c r="I5" s="5" t="s">
         <v>404</v>
       </c>
+      <c r="J5" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>937</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>389</v>
@@ -5927,13 +7256,19 @@
       <c r="I6" s="5" t="s">
         <v>408</v>
       </c>
+      <c r="J6" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>409</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>410</v>
+        <v>938</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>389</v>
@@ -5954,13 +7289,19 @@
       <c r="I7" s="5" t="s">
         <v>412</v>
       </c>
+      <c r="J7" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>414</v>
+        <v>939</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>389</v>
@@ -5981,13 +7322,19 @@
       <c r="I8" s="5" t="s">
         <v>416</v>
       </c>
+      <c r="J8" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>417</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>418</v>
+        <v>940</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>389</v>
@@ -6008,13 +7355,19 @@
       <c r="I9" s="5" t="s">
         <v>420</v>
       </c>
+      <c r="J9" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>984</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>421</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>422</v>
+        <v>941</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>389</v>
@@ -6035,13 +7388,19 @@
       <c r="I10" s="5" t="s">
         <v>424</v>
       </c>
+      <c r="J10" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>985</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>426</v>
+        <v>942</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>389</v>
@@ -6062,13 +7421,19 @@
       <c r="I11" s="5" t="s">
         <v>428</v>
       </c>
+      <c r="J11" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>986</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>429</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>430</v>
+        <v>943</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>389</v>
@@ -6089,13 +7454,19 @@
       <c r="I12" s="5" t="s">
         <v>432</v>
       </c>
+      <c r="J12" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>987</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>433</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>434</v>
+        <v>944</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>389</v>
@@ -6116,6 +7487,12 @@
       <c r="I13" s="5" t="s">
         <v>436</v>
       </c>
+      <c r="J13" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>988</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -6149,7 +7526,7 @@
         <v>441</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>442</v>
+        <v>945</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>389</v>
@@ -6170,13 +7547,19 @@
       <c r="I15" s="5" t="s">
         <v>444</v>
       </c>
+      <c r="J15" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>989</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>445</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>446</v>
+        <v>946</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>389</v>
@@ -6197,13 +7580,19 @@
       <c r="I16" s="5" t="s">
         <v>449</v>
       </c>
+      <c r="J16" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>990</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>450</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>451</v>
+        <v>947</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>389</v>
@@ -6224,13 +7613,19 @@
       <c r="I17" s="5" t="s">
         <v>453</v>
       </c>
+      <c r="J17" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>991</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>454</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>455</v>
+        <v>948</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>389</v>
@@ -6251,13 +7646,19 @@
       <c r="I18" s="5" t="s">
         <v>457</v>
       </c>
+      <c r="J18" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>992</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>458</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>459</v>
+        <v>949</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>389</v>
@@ -6278,13 +7679,19 @@
       <c r="I19" s="5" t="s">
         <v>461</v>
       </c>
+      <c r="J19" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>993</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>462</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>463</v>
+        <v>950</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>389</v>
@@ -6305,13 +7712,19 @@
       <c r="I20" s="5" t="s">
         <v>465</v>
       </c>
+      <c r="J20" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>466</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>467</v>
+        <v>951</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>389</v>
@@ -6332,13 +7745,19 @@
       <c r="I21" s="5" t="s">
         <v>469</v>
       </c>
+      <c r="J21" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>995</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>470</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>471</v>
+        <v>952</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>389</v>
@@ -6359,13 +7778,19 @@
       <c r="I22" s="5" t="s">
         <v>473</v>
       </c>
+      <c r="J22" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>996</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>474</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>475</v>
+        <v>953</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>389</v>
@@ -6386,13 +7811,19 @@
       <c r="I23" s="5" t="s">
         <v>477</v>
       </c>
+      <c r="J23" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>997</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>478</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>479</v>
+        <v>954</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>389</v>
@@ -6413,13 +7844,19 @@
       <c r="I24" s="5" t="s">
         <v>481</v>
       </c>
+      <c r="J24" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>998</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>482</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>483</v>
+        <v>955</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>389</v>
@@ -6440,13 +7877,19 @@
       <c r="I25" s="5" t="s">
         <v>485</v>
       </c>
+      <c r="J25" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>999</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>486</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>487</v>
+        <v>956</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>389</v>
@@ -6467,13 +7910,19 @@
       <c r="I26" s="5" t="s">
         <v>489</v>
       </c>
+      <c r="J26" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>1000</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>490</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>491</v>
+        <v>957</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>389</v>
@@ -6494,13 +7943,19 @@
       <c r="I27" s="5" t="s">
         <v>494</v>
       </c>
+      <c r="J27" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>1001</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>495</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>496</v>
+        <v>958</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>389</v>
@@ -6521,13 +7976,19 @@
       <c r="I28" s="5" t="s">
         <v>499</v>
       </c>
+      <c r="J28" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>1002</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>500</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>501</v>
+        <v>959</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>389</v>
@@ -6548,13 +8009,19 @@
       <c r="I29" s="5" t="s">
         <v>504</v>
       </c>
+      <c r="J29" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>1003</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>505</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>506</v>
+        <v>960</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>389</v>
@@ -6575,13 +8042,19 @@
       <c r="I30" s="5" t="s">
         <v>508</v>
       </c>
+      <c r="J30" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>1004</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>509</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>510</v>
+        <v>961</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>389</v>
@@ -6602,13 +8075,19 @@
       <c r="I31" s="5" t="s">
         <v>512</v>
       </c>
+      <c r="J31" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>1005</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>514</v>
+        <v>962</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>389</v>
@@ -6629,13 +8108,19 @@
       <c r="I32" s="5" t="s">
         <v>516</v>
       </c>
+      <c r="J32" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>1006</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
         <v>517</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>518</v>
+        <v>963</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>389</v>
@@ -6656,13 +8141,19 @@
       <c r="I33" s="5" t="s">
         <v>520</v>
       </c>
+      <c r="J33" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>1007</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>521</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>522</v>
+        <v>964</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>389</v>
@@ -6683,13 +8174,19 @@
       <c r="I34" s="5" t="s">
         <v>524</v>
       </c>
+      <c r="J34" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>1008</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>525</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>526</v>
+        <v>965</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>389</v>
@@ -6710,13 +8207,19 @@
       <c r="I35" s="5" t="s">
         <v>528</v>
       </c>
+      <c r="J35" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>1009</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>529</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>530</v>
+        <v>966</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>389</v>
@@ -6737,13 +8240,19 @@
       <c r="I36" s="5" t="s">
         <v>532</v>
       </c>
+      <c r="J36" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>1010</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>533</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>534</v>
+        <v>967</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>389</v>
@@ -6764,13 +8273,19 @@
       <c r="I37" s="5" t="s">
         <v>536</v>
       </c>
+      <c r="J37" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>1011</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>537</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>538</v>
+        <v>968</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>389</v>
@@ -6791,13 +8306,19 @@
       <c r="I38" s="5" t="s">
         <v>541</v>
       </c>
+      <c r="J38" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>1012</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
         <v>542</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>543</v>
+        <v>969</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>389</v>
@@ -6818,13 +8339,19 @@
       <c r="I39" s="5" t="s">
         <v>545</v>
       </c>
+      <c r="J39" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>1013</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>546</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>547</v>
+        <v>970</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>389</v>
@@ -6845,13 +8372,19 @@
       <c r="I40" s="5" t="s">
         <v>550</v>
       </c>
+      <c r="J40" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>1014</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>551</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>552</v>
+        <v>971</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>389</v>
@@ -6872,13 +8405,19 @@
       <c r="I41" s="5" t="s">
         <v>555</v>
       </c>
+      <c r="J41" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>1015</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>556</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>557</v>
+        <v>972</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>389</v>
@@ -6899,13 +8438,19 @@
       <c r="I42" s="5" t="s">
         <v>559</v>
       </c>
+      <c r="J42" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>1016</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>560</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>561</v>
+        <v>973</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>389</v>
@@ -6926,13 +8471,19 @@
       <c r="I43" s="5" t="s">
         <v>563</v>
       </c>
+      <c r="J43" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>1017</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
         <v>564</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>565</v>
+        <v>974</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>389</v>
@@ -6953,13 +8504,19 @@
       <c r="I44" s="5" t="s">
         <v>567</v>
       </c>
+      <c r="J44" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>1018</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>568</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>569</v>
+        <v>975</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>389</v>
@@ -6980,13 +8537,19 @@
       <c r="I45" s="5" t="s">
         <v>571</v>
       </c>
+      <c r="J45" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>1019</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
         <v>572</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>573</v>
+        <v>976</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>389</v>
@@ -7006,6 +8569,12 @@
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
         <v>576</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1020</v>
       </c>
     </row>
   </sheetData>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="1276">
   <si>
     <t xml:space="preserve">Card ID</t>
   </si>
@@ -3372,6 +3372,486 @@
   </si>
   <si>
     <t xml:space="preserve">Heat saved from old blows, spent now on the body that took them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 {damage|damage} to your opponent. {discard} 1 random card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 {damage|damage} to your opponent and give them 1 {burn}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 {damage|damage} to your opponent. {disrupt|They discard} 1 random component.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, your damaging spells deal +1 {damage|damage}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return up to 2 Verbal-providing components {recover|from your discard pile} to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{discard} 1 card. Deal 1 {damage|damage} to your opponent for each symbol on it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cost|Take 1 damage}. Deal 3 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 {damage|damage} to your opponent. {draw} 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 {damage|damage} to your opponent and 2 {damage|damage} to a {ward} they control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 5 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 {damage|damage} to your opponent. {prevent|Reactions cannot target} this spell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, deal 2 {damage|damage} to them. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{trap}: when your opponent {prevent|prevents} or reduces {damage|damage} you deal, deal 2 {damage|damage} to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{trap}: when your opponent attaches a Material (M) component to a prepared spell, deal 2 {damage|damage} to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent plays a Reaction, deal 4 {damage|damage} to them. The Reaction still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 6 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 {damage|damage} to your opponent. This {damage|damage} {prevent|cannot be reduced} below 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 {damage|damage} to your opponent and give them 2 {burn}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 {damage|damage} to your opponent. If they control a {ward}, 1 of that {damage|damage} hits the {ward} instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{discard} your hand. Deal 2 {damage|damage} to your opponent for each card {discard|discarded}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give your opponent 3 {burn}. This round, their {burn} also triggers at the start of your turns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, your damaging spells deal +2 {damage|damage} and you {cost|take 1 damage} at the start of each of your turns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 {damage|damage} to your opponent. {draw} 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 {damage|damage} to your opponent for each component attached to their prepared spells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 {damage|damage} to your opponent. This round, their Reactions {lock|cost 1 additional} component to play.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 {damage|damage} to your opponent, plus 1 for each {burn} on them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, deal {damage|damage} to them equal to its attached components. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell that requires a Material (M) component. Deal 2 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 {damage|damage} to your opponent. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent plays a Reaction, deal 3 {damage|damage} to them. The Reaction still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 7 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 {damage|damage} to your opponent, then 2 {damage|damage} to each {ward} they control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 5 {damage|damage} to your opponent. This spell {prevent|cannot be cancelled}, {cancel|redirected} or reduced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give your opponent 4 {burn}. This round, each of their {burn} deals 1 additional {damage|damage} when it triggers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 {damage|damage} to your opponent, plus 2 for each Reaction they have cast this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 {damage|damage} to your opponent. {draw} 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cost|Take 3 damage}. Deal 8 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy all of your opponent's {ward|Wards}. Deal {damage|damage} to them equal to the HP those {ward|Wards} had.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, whenever your opponent plays a Reaction, deal 3 {damage|damage} to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, deal {damage|damage} to them equal to twice its level. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When target spell deals {damage|damage} to you, deal twice that {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell or Reaction, deal 6 {damage|damage} to them. It still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 12 {damage|damage} to your opponent. This spell {prevent|cannot be cancelled}, {prevent|prevented}, {cancel|redirected} or reduced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 6 {damage|damage} to your opponent. This round, your damaging spells deal +2 {damage|damage} and your {burn} {empower|deals double}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When target spell deals {damage|damage} to you, deal three times that {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{draw} 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} 3 cards of your deck; take 1, put the rest back on top. This round, spell {damage|damage} dealt to you is {prevent|reduced by} 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} 2 cards of your deck; take 1, put the other on the bottom. {heal|Remove 1 Burn} from yourself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{prophecy} (2 turns): destroy your opponent's {unravel|largest Ward}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{draw} 2 cards. If either is a multi-symbol component, {draw|draw} a third.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return a component {recover|from your discard pile} to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 {damage|damage} to your opponent's {unravel|weakest Ward}. {scry|Look at the top} 2 cards of your deck and {scry|put them back} in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{reveal|Look at the components in your opponent's hand}. {disrupt|They discard} one of your choice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your opponent's {unravel|largest Ward} {unravel|loses half its HP}, rounded up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{draw} 1 card, then put a card from your hand on top of your deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 {damage|damage} to your opponent. {reveal|Look at their hand}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{prophecy} (2 turns): deal 2 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, {draw|draw} 1 card and deal 1 {damage|damage} to them. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return up to 2 components {recover|from your discard pile} to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Search your deck} for a component and put it into your hand, then shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{reveal|Look at your opponent's hand}. {draw} 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{discard} any number of cards, then {draw|draw} that many.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy target {ward} or ongoing effect. {draw} 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{prophecy} (2 turns): deal 4 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{draw} 2 cards, then put a card from your hand on top of your deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} 5 cards of your deck and {scry|put them back} in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} 3 cards of your deck and {scry|put them back} in any order. {prophecy} (1 turn): deal 2 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return a component attached to target spell {disrupt|to its owner's hand}. If the spell no longer meets its cost, {cancel|cancel} it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When your opponent casts a spell, {draw|draw} 1 card. The spell still resolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel|Redirect} target spell: it hits its caster instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{recover|Cast a copy} of a Level 1 spell you have already cast this round, without paying its cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shuffle your {discard|discard} pile into your deck, then {draw|draw} 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Search your deck} for any card and put it into your hand, then {draw|draw} 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} 5 cards of your deck; take 2, put the rest back on top in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{reveal|Look at your opponent's hand} and the top 3 cards of their deck. {draw} 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{prophecy} (3 turns): deal 7 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Search your deck} for up to 2 components and put them into your hand, then shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{draw|Draw until} you have 7 cards in hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell. It returns to its owner's prepared spells {seal|sealed}: it cannot be cast again this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell and return its components {disrupt|to its owner's hand}. The spell returns to their prepared spells unspent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{recover|Cast a copy} of a Level 1 or 2 spell either player has cast this round, without paying its cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{draw} 2 cards. Deal 1 {damage|damage} to your opponent for each card in your hand beyond 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{reveal|Look at your opponent's hand}. {disrupt|They discard} a card of your choice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{draw} 4 cards. This turn, your spells {prevent|cannot be cancelled} or {cancel|redirected}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return every component {recover|from your discard pile} to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Search your deck} for up to 3 cards and put them into your hand, then shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{prophecy} (3 turns): deal 9 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each player shuffles their hand and {discard|discard} pile into their deck, then {draw|draws} 5 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{recover|Cast a copy} of any spell cast this round, without paying its cost. You may cast 1 {empower|additional spell} this turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} 2 cards of your deck; take 1, put the other back on top.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} card of your deck: a component goes to your hand, anything else to the bottom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{discard} 1 card, then {draw|draw} 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return a component {recover|from your discard pile} to the top of your deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The next damaging spell you cast this turn deals +1 {damage|damage}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A {ward} you control gains 2 HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{discard} your hand, then {draw|draw} 4 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{discard} 1 card, then {scry|search your deck} for any card and put it into your hand; shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Search your deck} for a same-symbol dual component (VV, SS or MM) and put it into your hand, then shuffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} 4 cards of your deck and {scry|put them back} in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} card of your deck: a component attaches to one of your prepared spells, anything else goes to your hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cost|Take 2 damage}. This turn you may cast 1 {empower|additional spell}, if you have a free slot and its components are attached.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{heal} 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cost|Take 2 damage}. The next spell you cast this turn deals +3 {damage|damage}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 3 HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy target {ward} or ongoing effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{heal|Remove all Burn} from yourself. {heal} 1 for each {burn} removed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your spells {prevent|cannot be cancelled} or {cancel|redirected}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your opponent cannot make you {discard|discard} or {disrupt|strip} your cards or components.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shuffle your {discard|discard} pile into your deck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your opponent {lock|cannot draw} cards beyond their normal turn {draw|draw}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, whenever your opponent plays a Reaction, they {cost|take 2 damage}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{reveal|Look at your opponent's hand}. You may put a component from it {disrupt|on top of their deck}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A {ward} you control gains 2 HP (create a 2 HP {ward} if you have none). {heal|Remove 1 Burn} from yourself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 1 HP. If it is destroyed this round, {draw|draw} 2 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each {ward} you control gains 1 HP. If you control a {ward}, deal 1 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, spells with only 1 component attached {prevent|cannot target} you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, spell {damage|damage} dealt to you is {prevent|reduced by} 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target spell deals 1 {prevent|less damage}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target spell deals 1 {prevent|less damage}, or 2 less if you control a {ward}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target spell deals 1 {prevent|less damage}. {draw} 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{trap}: when your opponent attaches a component to a prepared spell, return that component {disrupt|to their hand}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{seal} target prepared spell your opponent controls: it cannot be cast this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{prevent} all {damage|damage} from target spell. {heal} half the {damage|damage} {prevent|prevented}, rounded down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 3 HP. Whenever it absorbs {damage|damage}, deal 1 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove all components from target spell; if it no longer meets its cost, {cancel|cancel} it. {cost|Your opponent draws} 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell. You may {empower|immediately attach} 1 component from your hand to a prepared spell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell that requires a Material (M) component.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell that requires a Somatic (S) component.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your opponent {lock|cannot play Reactions}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, your opponent's Reactions {lock|cost 1 additional} component to play.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 2 HP. While it stands, Level 1 spells {prevent|cannot target} you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 3 HP. While it stands, the first time each round your opponent casts a spell, {draw|draw} 1 card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cost|Sacrifice} one of your {ward|Wards}. {prevent} all {damage|damage} from target spell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 6 HP. This round, {damage|damage} dealt to you is {prevent|reduced by} 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell. Your opponent {lock|cannot cast} more spells this turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, spell {damage|damage} that would hit you {heal|heals} you instead (up to 5 HP).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each {ward} you control gains 2 HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell. Deal 2 {damage|damage} to your opponent for each component attached to it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 5 HP. When it is destroyed, create a {ward} with 2 HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{disrupt|Strip} every component from your opponent's prepared spells; {cancel|cancel} target spell if it no longer meets its cost. They {draw|draw} 1 card per spell stripped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 4 HP. This round, your opponent {prevent|cannot target} or destroy your {ward|Wards}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy one of your {ward|Wards}. Deal {damage|damage} equal to its remaining HP to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal {damage|damage} to your opponent equal to half your {ledger|ledger}, rounded up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 3 {damage|damage} to your opponent for each Reaction you have played this round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, whenever your opponent plays a Reaction, they {cost|take 3 damage}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 5 {damage|damage} to your opponent, or 7 if you control a {ward}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cost|Sacrifice} all your {ward|Wards}. Deal 2 {damage|damage} to your opponent for each HP they had.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} target spell. Deal twice the {damage|damage} it would have dealt to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 {damage|damage} to your opponent. If they control a {ward}, destroy it and deal 8 {damage|damage} instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, spells {prevent|cannot damage you} and your opponent {lock|cannot play Reactions}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 10 HP that your opponent {prevent|cannot target} or destroy. When it breaks, {heal|heal} 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} every spell on the stack. Your opponent {lock|cannot cast} spells this turn or play Reactions until the start of your next turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal {damage|damage} to your opponent equal to your current HP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 {damage|damage} to your opponent for each round of this match so far.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cancel} every spell your opponent has on the stack. Deal 3 {damage|damage} to them for each spell {cancel|cancelled}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy every {ward} on both sides. Deal 3 {damage|damage} to your opponent for each {ward} destroyed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend up to 4 from your {ledger|ledger}. Create a {ward} with HP equal to the amount spent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 6 from your {ledger|ledger} to {cancel|cancel} target spell. Castable only with 6 or more banked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend up to 6 from your {ledger|ledger}. {heal} half the amount spent, rounded down.</t>
   </si>
 </sst>
 </file>
@@ -3847,7 +4327,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>828</v>
+        <v>1229</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="5" t="s">
@@ -3880,7 +4360,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>829</v>
+        <v>1230</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="5" t="s">
@@ -3913,7 +4393,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>830</v>
+        <v>1231</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="5" t="s">
@@ -3946,7 +4426,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>831</v>
+        <v>1232</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="5" t="s">
@@ -3979,7 +4459,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>832</v>
+        <v>1233</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="5" t="s">
@@ -4012,7 +4492,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>833</v>
+        <v>1234</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="5" t="s">
@@ -4045,7 +4525,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>834</v>
+        <v>1235</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="5" t="s">
@@ -4078,7 +4558,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>835</v>
+        <v>1236</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="5" t="s">
@@ -4111,7 +4591,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>836</v>
+        <v>1237</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="5" t="s">
@@ -4144,7 +4624,7 @@
         <v>51</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>837</v>
+        <v>1238</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="5" t="s">
@@ -4177,7 +4657,7 @@
         <v>51</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>838</v>
+        <v>1239</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="5" t="s">
@@ -4210,7 +4690,7 @@
         <v>51</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>839</v>
+        <v>1240</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="5" t="s">
@@ -4243,7 +4723,7 @@
         <v>51</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>840</v>
+        <v>1241</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="5" t="s">
@@ -4276,7 +4756,7 @@
         <v>51</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>841</v>
+        <v>1242</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="5" t="s">
@@ -4309,7 +4789,7 @@
         <v>72</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>842</v>
+        <v>1243</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="5" t="s">
@@ -4342,7 +4822,7 @@
         <v>51</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>843</v>
+        <v>1244</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="5" t="s">
@@ -4375,7 +4855,7 @@
         <v>51</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>844</v>
+        <v>1245</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="5" t="s">
@@ -4408,7 +4888,7 @@
         <v>51</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>845</v>
+        <v>1246</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="5" t="s">
@@ -4441,7 +4921,7 @@
         <v>51</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>846</v>
+        <v>1247</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="5" t="s">
@@ -4474,7 +4954,7 @@
         <v>93</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>847</v>
+        <v>1248</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="5" t="s">
@@ -4507,7 +4987,7 @@
         <v>51</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>848</v>
+        <v>1249</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="5" t="s">
@@ -4540,7 +5020,7 @@
         <v>102</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>849</v>
+        <v>1250</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="5" t="s">
@@ -4573,7 +5053,7 @@
         <v>102</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>850</v>
+        <v>1251</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="5" t="s">
@@ -4606,7 +5086,7 @@
         <v>111</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>851</v>
+        <v>1252</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="5" t="s">
@@ -4639,7 +5119,7 @@
         <v>102</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>852</v>
+        <v>1253</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="5" t="s">
@@ -4672,7 +5152,7 @@
         <v>120</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>853</v>
+        <v>1254</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="5" t="s">
@@ -4705,7 +5185,7 @@
         <v>111</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>854</v>
+        <v>1255</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="5" t="s">
@@ -4738,7 +5218,7 @@
         <v>102</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>855</v>
+        <v>1256</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="5" t="s">
@@ -4771,7 +5251,7 @@
         <v>102</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>856</v>
+        <v>1257</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="5" t="s">
@@ -4804,7 +5284,7 @@
         <v>111</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>837</v>
+        <v>1238</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="5" t="s">
@@ -4837,7 +5317,7 @@
         <v>102</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>857</v>
+        <v>1258</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="5" t="s">
@@ -4870,7 +5350,7 @@
         <v>51</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>858</v>
+        <v>1259</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="5" t="s">
@@ -4903,7 +5383,7 @@
         <v>111</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>859</v>
+        <v>1260</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="5" t="s">
@@ -4936,7 +5416,7 @@
         <v>102</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>860</v>
+        <v>1261</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="5" t="s">
@@ -4969,7 +5449,7 @@
         <v>102</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>861</v>
+        <v>1262</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="5" t="s">
@@ -5002,7 +5482,7 @@
         <v>120</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>862</v>
+        <v>1263</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="5" t="s">
@@ -5035,7 +5515,7 @@
         <v>102</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>863</v>
+        <v>1264</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="5" t="s">
@@ -5068,7 +5548,7 @@
         <v>111</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>864</v>
+        <v>1265</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="5" t="s">
@@ -5101,7 +5581,7 @@
         <v>173</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>865</v>
+        <v>1266</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="5" t="s">
@@ -5134,7 +5614,7 @@
         <v>178</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>866</v>
+        <v>1267</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="5" t="s">
@@ -5167,7 +5647,7 @@
         <v>173</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>867</v>
+        <v>1268</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="5" t="s">
@@ -5200,7 +5680,7 @@
         <v>173</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>868</v>
+        <v>1269</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="5" t="s">
@@ -5233,7 +5713,7 @@
         <v>178</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>869</v>
+        <v>1270</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="5" t="s">
@@ -5266,7 +5746,7 @@
         <v>173</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>870</v>
+        <v>1271</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="5" t="s">
@@ -5299,7 +5779,7 @@
         <v>173</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>871</v>
+        <v>1272</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
@@ -5340,7 +5820,7 @@
         </is>
       </c>
       <c r="G47" s="5" t="s">
-        <v>872</v>
+        <v>1273</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="5" t="inlineStr">
@@ -5383,7 +5863,7 @@
         </is>
       </c>
       <c r="G48" s="5" t="s">
-        <v>873</v>
+        <v>1274</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="5" t="inlineStr">
@@ -5426,7 +5906,7 @@
         </is>
       </c>
       <c r="G49" s="5" t="s">
-        <v>874</v>
+        <v>1275</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="5" t="inlineStr">
@@ -5526,7 +6006,7 @@
         <v>204</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>714</v>
+        <v>1116</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="5" t="s">
@@ -5559,7 +6039,7 @@
         <v>204</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>715</v>
+        <v>1117</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="5" t="s">
@@ -5592,7 +6072,7 @@
         <v>204</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>716</v>
+        <v>1118</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="5" t="s">
@@ -5625,7 +6105,7 @@
         <v>204</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>717</v>
+        <v>1119</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="5"/>
@@ -5656,7 +6136,7 @@
         <v>204</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>718</v>
+        <v>1120</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="5"/>
@@ -5687,7 +6167,7 @@
         <v>204</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>719</v>
+        <v>1121</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="5"/>
@@ -5718,7 +6198,7 @@
         <v>204</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>720</v>
+        <v>1122</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="5" t="s">
@@ -5751,7 +6231,7 @@
         <v>204</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>721</v>
+        <v>1123</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="5"/>
@@ -5782,7 +6262,7 @@
         <v>233</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>722</v>
+        <v>1124</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="5" t="s">
@@ -5815,7 +6295,7 @@
         <v>204</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>723</v>
+        <v>1125</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="5"/>
@@ -5846,7 +6326,7 @@
         <v>241</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>724</v>
+        <v>1126</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="5"/>
@@ -5877,7 +6357,7 @@
         <v>241</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>725</v>
+        <v>1127</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="5" t="s">
@@ -5910,7 +6390,7 @@
         <v>204</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>726</v>
+        <v>1128</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="5"/>
@@ -5941,7 +6421,7 @@
         <v>204</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>727</v>
+        <v>1129</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="5" t="s">
@@ -5974,7 +6454,7 @@
         <v>204</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>728</v>
+        <v>1130</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="5" t="s">
@@ -6007,7 +6487,7 @@
         <v>241</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>729</v>
+        <v>1131</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="5"/>
@@ -6038,7 +6518,7 @@
         <v>241</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>730</v>
+        <v>1132</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="5" t="s">
@@ -6071,7 +6551,7 @@
         <v>241</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>731</v>
+        <v>1133</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="5" t="s">
@@ -6104,7 +6584,7 @@
         <v>241</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>732</v>
+        <v>1134</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="5"/>
@@ -6135,7 +6615,7 @@
         <v>241</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>733</v>
+        <v>1135</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="5" t="s">
@@ -6168,7 +6648,7 @@
         <v>241</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>734</v>
+        <v>1136</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="5" t="s">
@@ -6201,7 +6681,7 @@
         <v>241</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>735</v>
+        <v>1137</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="5" t="s">
@@ -6234,7 +6714,7 @@
         <v>241</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>736</v>
+        <v>1138</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="5" t="s">
@@ -6267,7 +6747,7 @@
         <v>233</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>737</v>
+        <v>1139</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="5" t="s">
@@ -6300,7 +6780,7 @@
         <v>241</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>738</v>
+        <v>1140</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="5" t="s">
@@ -6333,7 +6813,7 @@
         <v>93</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>739</v>
+        <v>1141</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="5" t="s">
@@ -6366,7 +6846,7 @@
         <v>241</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>740</v>
+        <v>1142</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="5" t="s">
@@ -6399,7 +6879,7 @@
         <v>241</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>741</v>
+        <v>1143</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="5" t="s">
@@ -6432,7 +6912,7 @@
         <v>233</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>742</v>
+        <v>1144</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="5" t="s">
@@ -6465,7 +6945,7 @@
         <v>241</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>743</v>
+        <v>1145</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="5"/>
@@ -6496,7 +6976,7 @@
         <v>241</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>744</v>
+        <v>1146</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="5" t="s">
@@ -6529,7 +7009,7 @@
         <v>321</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>745</v>
+        <v>1147</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="5" t="s">
@@ -6562,7 +7042,7 @@
         <v>321</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>746</v>
+        <v>1148</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="5" t="s">
@@ -6595,7 +7075,7 @@
         <v>321</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>734</v>
+        <v>1136</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="5" t="s">
@@ -6628,7 +7108,7 @@
         <v>321</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>747</v>
+        <v>1149</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="5" t="s">
@@ -6661,7 +7141,7 @@
         <v>321</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>748</v>
+        <v>1150</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="5" t="s">
@@ -6694,7 +7174,7 @@
         <v>321</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>749</v>
+        <v>1151</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="5" t="s">
@@ -6727,7 +7207,7 @@
         <v>346</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>750</v>
+        <v>1152</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="5" t="s">
@@ -6760,7 +7240,7 @@
         <v>321</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>751</v>
+        <v>1153</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="5" t="s">
@@ -6793,7 +7273,7 @@
         <v>321</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>752</v>
+        <v>1154</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="5" t="s">
@@ -6826,7 +7306,7 @@
         <v>359</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>753</v>
+        <v>1155</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="5" t="s">
@@ -6859,7 +7339,7 @@
         <v>321</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>754</v>
+        <v>1156</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="5" t="s">
@@ -6892,7 +7372,7 @@
         <v>346</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>755</v>
+        <v>1157</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="5"/>
@@ -6923,7 +7403,7 @@
         <v>321</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>756</v>
+        <v>1158</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="5"/>
@@ -6954,7 +7434,7 @@
         <v>374</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>757</v>
+        <v>1159</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
@@ -6987,7 +7467,7 @@
         <v>379</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>758</v>
+        <v>1160</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="5" t="s">
@@ -7020,7 +7500,7 @@
         <v>384</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>759</v>
+        <v>1161</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="5" t="s">
@@ -7118,7 +7598,7 @@
         <v>390</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>760</v>
+        <v>1162</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="5" t="s">
@@ -7151,7 +7631,7 @@
         <v>390</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>761</v>
+        <v>1163</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="5" t="s">
@@ -7184,7 +7664,7 @@
         <v>390</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>762</v>
+        <v>1164</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="5" t="s">
@@ -7217,7 +7697,7 @@
         <v>390</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>763</v>
+        <v>1165</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="5" t="s">
@@ -7250,7 +7730,7 @@
         <v>390</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>764</v>
+        <v>1166</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="5" t="s">
@@ -7283,7 +7763,7 @@
         <v>390</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>765</v>
+        <v>1167</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="5" t="s">
@@ -7316,7 +7796,7 @@
         <v>390</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>766</v>
+        <v>1168</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="5" t="s">
@@ -7349,7 +7829,7 @@
         <v>390</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>767</v>
+        <v>1169</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="5" t="s">
@@ -7382,7 +7862,7 @@
         <v>390</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>768</v>
+        <v>1170</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="5" t="s">
@@ -7415,7 +7895,7 @@
         <v>390</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>769</v>
+        <v>1171</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="5" t="s">
@@ -7448,7 +7928,7 @@
         <v>390</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>770</v>
+        <v>1172</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="5" t="s">
@@ -7481,7 +7961,7 @@
         <v>447</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>771</v>
+        <v>1173</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="5" t="s">
@@ -7541,7 +8021,7 @@
         <v>390</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>772</v>
+        <v>1174</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="5" t="s">
@@ -7574,7 +8054,7 @@
         <v>447</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>773</v>
+        <v>1175</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="5" t="s">
@@ -7607,7 +8087,7 @@
         <v>447</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>774</v>
+        <v>1176</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="5" t="s">
@@ -7640,7 +8120,7 @@
         <v>447</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>775</v>
+        <v>1177</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="5" t="s">
@@ -7673,7 +8153,7 @@
         <v>447</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>776</v>
+        <v>1178</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="5" t="s">
@@ -7706,7 +8186,7 @@
         <v>447</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>777</v>
+        <v>1179</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="5" t="s">
@@ -7739,7 +8219,7 @@
         <v>447</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>778</v>
+        <v>1180</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="5" t="s">
@@ -7772,7 +8252,7 @@
         <v>447</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>779</v>
+        <v>1181</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="5" t="s">
@@ -7805,7 +8285,7 @@
         <v>447</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>780</v>
+        <v>1182</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="5" t="s">
@@ -7838,7 +8318,7 @@
         <v>447</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>781</v>
+        <v>1183</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="5" t="s">
@@ -7871,7 +8351,7 @@
         <v>447</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>782</v>
+        <v>1184</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="5" t="s">
@@ -7904,7 +8384,7 @@
         <v>447</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>783</v>
+        <v>1185</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="5" t="s">
@@ -7937,7 +8417,7 @@
         <v>492</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>784</v>
+        <v>1186</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="5" t="s">
@@ -7970,7 +8450,7 @@
         <v>497</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>785</v>
+        <v>1187</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="5" t="s">
@@ -8003,7 +8483,7 @@
         <v>502</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>786</v>
+        <v>1188</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="5" t="s">
@@ -8036,7 +8516,7 @@
         <v>502</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>787</v>
+        <v>1189</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="5" t="s">
@@ -8069,7 +8549,7 @@
         <v>502</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>788</v>
+        <v>1190</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="5" t="s">
@@ -8102,7 +8582,7 @@
         <v>502</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>789</v>
+        <v>1191</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="5" t="s">
@@ -8135,7 +8615,7 @@
         <v>502</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>790</v>
+        <v>1192</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="5" t="s">
@@ -8168,7 +8648,7 @@
         <v>502</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>791</v>
+        <v>1193</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="5" t="s">
@@ -8201,7 +8681,7 @@
         <v>502</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>792</v>
+        <v>1194</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="5" t="s">
@@ -8234,7 +8714,7 @@
         <v>502</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>793</v>
+        <v>1195</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="5" t="s">
@@ -8267,7 +8747,7 @@
         <v>502</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>794</v>
+        <v>1196</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="5" t="s">
@@ -8300,7 +8780,7 @@
         <v>539</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>795</v>
+        <v>1197</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="5" t="s">
@@ -8333,7 +8813,7 @@
         <v>539</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>796</v>
+        <v>1198</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="5" t="s">
@@ -8366,7 +8846,7 @@
         <v>548</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>797</v>
+        <v>1199</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="5" t="s">
@@ -8399,7 +8879,7 @@
         <v>553</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>798</v>
+        <v>1200</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="5" t="s">
@@ -8432,7 +8912,7 @@
         <v>553</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>799</v>
+        <v>1201</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="5" t="s">
@@ -8465,7 +8945,7 @@
         <v>553</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>800</v>
+        <v>1202</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="5" t="s">
@@ -8498,7 +8978,7 @@
         <v>553</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>801</v>
+        <v>1203</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="5" t="s">
@@ -8531,7 +9011,7 @@
         <v>553</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>802</v>
+        <v>1204</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="5" t="s">
@@ -8564,7 +9044,7 @@
         <v>574</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>803</v>
+        <v>1205</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="5" t="s">
@@ -8652,7 +9132,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="5" t="s">
-        <v>804</v>
+        <v>1206</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>582</v>
@@ -8677,7 +9157,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="5" t="s">
-        <v>805</v>
+        <v>1207</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>587</v>
@@ -8702,7 +9182,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5" t="s">
-        <v>769</v>
+        <v>1171</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>587</v>
@@ -8727,7 +9207,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="5" t="s">
-        <v>806</v>
+        <v>1208</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>596</v>
@@ -8777,7 +9257,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="5" t="s">
-        <v>808</v>
+        <v>1209</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>606</v>
@@ -8802,7 +9282,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="5" t="s">
-        <v>809</v>
+        <v>1210</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>611</v>
@@ -8827,7 +9307,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="5" t="s">
-        <v>810</v>
+        <v>1211</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>616</v>
@@ -8911,7 +9391,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="5" t="s">
-        <v>779</v>
+        <v>1181</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>622</v>
@@ -8936,7 +9416,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="5" t="s">
-        <v>811</v>
+        <v>1212</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>627</v>
@@ -8961,7 +9441,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5" t="s">
-        <v>812</v>
+        <v>1213</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>582</v>
@@ -8986,7 +9466,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="5" t="s">
-        <v>813</v>
+        <v>1214</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>636</v>
@@ -9011,7 +9491,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="5" t="s">
-        <v>765</v>
+        <v>1167</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>606</v>
@@ -9036,7 +9516,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="5" t="s">
-        <v>814</v>
+        <v>1215</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>644</v>
@@ -9061,7 +9541,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="5" t="s">
-        <v>815</v>
+        <v>1216</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>649</v>
@@ -9086,7 +9566,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="5" t="s">
-        <v>816</v>
+        <v>1217</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>654</v>
@@ -9111,7 +9591,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="5" t="s">
-        <v>817</v>
+        <v>1218</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>659</v>
@@ -9136,7 +9616,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="5" t="s">
-        <v>818</v>
+        <v>1219</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>611</v>
@@ -9161,7 +9641,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="5" t="s">
-        <v>819</v>
+        <v>1220</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>668</v>
@@ -9186,7 +9666,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="5" t="s">
-        <v>820</v>
+        <v>1221</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>673</v>
@@ -9211,7 +9691,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="5" t="s">
-        <v>821</v>
+        <v>1222</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>678</v>
@@ -9236,7 +9716,7 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="5" t="s">
-        <v>822</v>
+        <v>1223</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>683</v>
@@ -9261,7 +9741,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="5" t="s">
-        <v>823</v>
+        <v>1224</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>688</v>
@@ -9286,7 +9766,7 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="5" t="s">
-        <v>824</v>
+        <v>1225</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>693</v>
@@ -9311,7 +9791,7 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="5" t="s">
-        <v>825</v>
+        <v>1226</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>698</v>
@@ -9336,7 +9816,7 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="5" t="s">
-        <v>826</v>
+        <v>1227</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>683</v>
@@ -9361,7 +9841,7 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="5" t="s">
-        <v>771</v>
+        <v>1173</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>707</v>
@@ -9386,7 +9866,7 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="5" t="s">
-        <v>827</v>
+        <v>1228</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>712</v>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="1292">
   <si>
     <t xml:space="preserve">Card ID</t>
   </si>
@@ -3852,6 +3852,54 @@
   </si>
   <si>
     <t xml:space="preserve">Spend up to 6 from your {ledger|ledger}. {heal} half the amount spent, rounded down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{trap}: when your opponent {prevent|prevents} or reduces damage you deal, deal 2 {damage|damage} to them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 4 {damage|damage} to your opponent. This damage {prevent|cannot be reduced} below 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, your damaging spells deal {empower|+2 damage} and you {cost|take 1 damage} at the start of each of your turns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{discard} your hand. Deal 2 {damage|damage} to your opponent for each card discarded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{scry|Look at the top} 3 cards of your deck; take 1, put the rest back on top. This round, spell damage dealt to you is {prevent|reduced by} 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each player shuffles their hand and discard pile into their deck, then {draw|draws} 5 cards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, whenever your opponent plays a Reaction, they take 2 {damage|damage}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your opponent {lock|cannot draw} cards beyond their normal turn draw.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the start of your next turn, your opponent cannot make you discard or {disrupt|strip} your cards or components.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, whenever your opponent plays a Reaction, they take 3 {damage|damage}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This round, spell damage dealt to you is {prevent|reduced by} 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 6 HP. This round, damage dealt to you is {prevent|reduced by} 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{prevent} all damage from target spell. {heal} half the damage {prevent|prevented}, rounded down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{cost|Sacrifice} one of your {ward|Wards}. {prevent} all damage from target spell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a {ward} with 3 HP. Whenever it absorbs damage, deal 1 {damage|damage} to your opponent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{disrupt|Strip} every component from your opponent's prepared spells; {cancel|cancel} target spell if it no longer meets its cost. They draw 1 card per spell stripped.</t>
   </si>
 </sst>
 </file>
@@ -4459,7 +4507,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>1233</v>
+        <v>1286</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="5" t="s">
@@ -4657,7 +4705,7 @@
         <v>51</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>1239</v>
+        <v>1288</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="5" t="s">
@@ -4690,7 +4738,7 @@
         <v>51</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1240</v>
+        <v>1290</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="5" t="s">
@@ -4987,7 +5035,7 @@
         <v>51</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>1249</v>
+        <v>1289</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="5" t="s">
@@ -5020,7 +5068,7 @@
         <v>102</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>1250</v>
+        <v>1287</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="5" t="s">
@@ -5218,7 +5266,7 @@
         <v>102</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>1256</v>
+        <v>1291</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="5" t="s">
@@ -5416,7 +5464,7 @@
         <v>102</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>1261</v>
+        <v>1285</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="5" t="s">
@@ -6421,7 +6469,7 @@
         <v>204</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>1129</v>
+        <v>1276</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="5" t="s">
@@ -6551,7 +6599,7 @@
         <v>241</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1133</v>
+        <v>1277</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="5" t="s">
@@ -6648,7 +6696,7 @@
         <v>241</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>1136</v>
+        <v>1279</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="5" t="s">
@@ -6714,7 +6762,7 @@
         <v>241</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>1138</v>
+        <v>1278</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="5" t="s">
@@ -7075,7 +7123,7 @@
         <v>321</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>1136</v>
+        <v>1279</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="5" t="s">
@@ -7631,7 +7679,7 @@
         <v>390</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>1163</v>
+        <v>1280</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="5" t="s">
@@ -9011,7 +9059,7 @@
         <v>553</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>1204</v>
+        <v>1281</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="5" t="s">
@@ -9741,7 +9789,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="5" t="s">
-        <v>1224</v>
+        <v>1284</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>688</v>
@@ -9791,7 +9839,7 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="5" t="s">
-        <v>1226</v>
+        <v>1283</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>698</v>
@@ -9816,7 +9864,7 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="5" t="s">
-        <v>1227</v>
+        <v>1282</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>683</v>

--- a/ibokki_spell_cards.xlsx
+++ b/ibokki_spell_cards.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="1293">
   <si>
     <t xml:space="preserve">Card ID</t>
   </si>
@@ -3900,6 +3900,9 @@
   </si>
   <si>
     <t xml:space="preserve">{disrupt|Strip} every component from your opponent's prepared spells; {cancel|cancel} target spell if it no longer meets its cost. They draw 1 card per spell stripped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -4385,7 +4388,7 @@
         <v>884</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>1068</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4418,7 +4421,7 @@
         <v>884</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>1069</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4451,7 +4454,7 @@
         <v>884</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>1070</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4484,7 +4487,7 @@
         <v>884</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>1071</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4517,7 +4520,7 @@
         <v>884</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>1072</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4550,7 +4553,7 @@
         <v>884</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>1073</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4583,7 +4586,7 @@
         <v>884</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>1074</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4616,7 +4619,7 @@
         <v>884</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>1075</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4649,7 +4652,7 @@
         <v>884</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>1076</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4682,7 +4685,7 @@
         <v>884</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>1077</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4715,7 +4718,7 @@
         <v>884</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>1078</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4748,7 +4751,7 @@
         <v>884</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>1079</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4781,7 +4784,7 @@
         <v>884</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>1080</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4814,7 +4817,7 @@
         <v>884</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>1081</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4847,7 +4850,7 @@
         <v>884</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>1082</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4880,7 +4883,7 @@
         <v>884</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>1083</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4913,7 +4916,7 @@
         <v>884</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>1084</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4946,7 +4949,7 @@
         <v>884</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>1085</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4979,7 +4982,7 @@
         <v>884</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>1086</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5012,7 +5015,7 @@
         <v>884</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>1087</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5045,7 +5048,7 @@
         <v>884</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>1088</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5078,7 +5081,7 @@
         <v>884</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>1089</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5111,7 +5114,7 @@
         <v>884</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>1090</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5144,7 +5147,7 @@
         <v>884</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>1091</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5177,7 +5180,7 @@
         <v>884</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>1092</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5210,7 +5213,7 @@
         <v>884</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>1093</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5243,7 +5246,7 @@
         <v>884</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1094</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5276,7 +5279,7 @@
         <v>884</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>1095</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5309,7 +5312,7 @@
         <v>884</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>1096</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5342,7 +5345,7 @@
         <v>884</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>1097</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5375,7 +5378,7 @@
         <v>884</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>1098</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5408,7 +5411,7 @@
         <v>884</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>1099</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5441,7 +5444,7 @@
         <v>884</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>1100</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5474,7 +5477,7 @@
         <v>884</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>1101</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5507,7 +5510,7 @@
         <v>884</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>1102</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5540,7 +5543,7 @@
         <v>884</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>1103</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5573,7 +5576,7 @@
         <v>884</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>1104</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5606,7 +5609,7 @@
         <v>884</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>1105</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5639,7 +5642,7 @@
         <v>884</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>1106</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5672,7 +5675,7 @@
         <v>884</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>1107</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5705,7 +5708,7 @@
         <v>884</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>1108</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5738,7 +5741,7 @@
         <v>884</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>1109</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5771,7 +5774,7 @@
         <v>884</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>1110</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5804,7 +5807,7 @@
         <v>884</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>1111</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5837,7 +5840,7 @@
         <v>884</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>1112</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5880,7 +5883,7 @@
         <v>884</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>1113</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5923,7 +5926,7 @@
         <v>884</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>1114</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5966,7 +5969,7 @@
         <v>884</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>1115</v>
+        <v>1292</v>
       </c>
     </row>
   </sheetData>
@@ -6064,7 +6067,7 @@
         <v>884</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>886</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6097,7 +6100,7 @@
         <v>884</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>887</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6130,7 +6133,7 @@
         <v>884</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>888</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6161,7 +6164,7 @@
         <v>884</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>889</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6192,7 +6195,7 @@
         <v>884</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>890</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6223,7 +6226,7 @@
         <v>884</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>891</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6256,7 +6259,7 @@
         <v>884</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>892</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6287,7 +6290,7 @@
         <v>884</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>893</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6320,7 +6323,7 @@
         <v>884</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>894</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6351,7 +6354,7 @@
         <v>884</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>895</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6382,7 +6385,7 @@
         <v>884</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>896</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6415,7 +6418,7 @@
         <v>884</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>897</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6446,7 +6449,7 @@
         <v>884</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>898</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6479,7 +6482,7 @@
         <v>884</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>899</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6512,7 +6515,7 @@
         <v>884</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>900</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6543,7 +6546,7 @@
         <v>884</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>901</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6576,7 +6579,7 @@
         <v>884</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>902</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6609,7 +6612,7 @@
         <v>884</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>903</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6640,7 +6643,7 @@
         <v>884</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>904</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6673,7 +6676,7 @@
         <v>884</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>905</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6706,7 +6709,7 @@
         <v>884</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>906</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6739,7 +6742,7 @@
         <v>884</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>907</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6772,7 +6775,7 @@
         <v>884</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>908</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6805,7 +6808,7 @@
         <v>884</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>909</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6838,7 +6841,7 @@
         <v>884</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>910</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6871,7 +6874,7 @@
         <v>884</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>911</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6904,7 +6907,7 @@
         <v>884</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>912</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6937,7 +6940,7 @@
         <v>884</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>913</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6970,7 +6973,7 @@
         <v>884</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>914</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7001,7 +7004,7 @@
         <v>884</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>915</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7034,7 +7037,7 @@
         <v>884</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>916</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7067,7 +7070,7 @@
         <v>884</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>917</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7100,7 +7103,7 @@
         <v>884</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>918</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7133,7 +7136,7 @@
         <v>884</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>919</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7166,7 +7169,7 @@
         <v>884</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>920</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7199,7 +7202,7 @@
         <v>884</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>921</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7232,7 +7235,7 @@
         <v>884</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>922</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7265,7 +7268,7 @@
         <v>884</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>923</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7298,7 +7301,7 @@
         <v>884</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>924</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7331,7 +7334,7 @@
         <v>884</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>925</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7364,7 +7367,7 @@
         <v>884</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>926</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7397,7 +7400,7 @@
         <v>884</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>927</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7428,7 +7431,7 @@
         <v>884</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>928</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7459,7 +7462,7 @@
         <v>884</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>929</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7492,7 +7495,7 @@
         <v>884</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>930</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7525,7 +7528,7 @@
         <v>884</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>931</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7558,7 +7561,7 @@
         <v>884</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>932</v>
+        <v>1292</v>
       </c>
     </row>
   </sheetData>
@@ -7656,7 +7659,7 @@
         <v>884</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>977</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7689,7 +7692,7 @@
         <v>884</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>978</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7722,7 +7725,7 @@
         <v>884</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>979</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7755,7 +7758,7 @@
         <v>884</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>980</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7788,7 +7791,7 @@
         <v>884</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>981</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7821,7 +7824,7 @@
         <v>884</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>982</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7854,7 +7857,7 @@
         <v>884</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>983</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7887,7 +7890,7 @@
         <v>884</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>984</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7920,7 +7923,7 @@
         <v>884</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>985</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7953,7 +7956,7 @@
         <v>884</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>986</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7986,7 +7989,7 @@
         <v>884</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>987</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8019,7 +8022,7 @@
         <v>884</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>988</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8079,7 +8082,7 @@
         <v>884</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>989</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8112,7 +8115,7 @@
         <v>884</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>990</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8145,7 +8148,7 @@
         <v>884</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>991</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8178,7 +8181,7 @@
         <v>884</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>992</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8211,7 +8214,7 @@
         <v>884</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>993</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8244,7 +8247,7 @@
         <v>884</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>994</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8277,7 +8280,7 @@
         <v>884</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>995</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8310,7 +8313,7 @@
         <v>884</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>996</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8343,7 +8346,7 @@
         <v>884</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>997</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8376,7 +8379,7 @@
         <v>884</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>998</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8409,7 +8412,7 @@
         <v>884</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>999</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8442,7 +8445,7 @@
         <v>884</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>1000</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8475,7 +8478,7 @@
         <v>884</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>1001</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8508,7 +8511,7 @@
         <v>884</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1002</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8541,7 +8544,7 @@
         <v>884</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>1003</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8574,7 +8577,7 @@
         <v>884</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>1004</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8607,7 +8610,7 @@
         <v>884</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>1005</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8640,7 +8643,7 @@
         <v>884</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>1006</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8673,7 +8676,7 @@
         <v>884</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>1007</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8706,7 +8709,7 @@
         <v>884</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>1008</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8739,7 +8742,7 @@
         <v>884</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>1009</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8772,7 +8775,7 @@
         <v>884</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>1010</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8805,7 +8808,7 @@
         <v>884</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>1011</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8838,7 +8841,7 @@
         <v>884</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>1012</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8871,7 +8874,7 @@
         <v>884</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>1013</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8904,7 +8907,7 @@
         <v>884</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>1014</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8937,7 +8940,7 @@
         <v>884</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>1015</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8970,7 +8973,7 @@
         <v>884</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>1016</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9003,7 +9006,7 @@
         <v>884</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>1017</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9036,7 +9039,7 @@
         <v>884</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>1018</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9069,7 +9072,7 @@
         <v>884</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>1019</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9102,7 +9105,7 @@
         <v>884</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>1020</v>
+        <v>1292</v>
       </c>
     </row>
   </sheetData>
